--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,6 +990,3842 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127482681</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78681</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>353</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>592639</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7031884</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127482288</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>592543</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7031902</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127483367</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>592559</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7031863</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127481318</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75130</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>308</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>592760</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7031963</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127481272</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>592774</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7031974</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127481815</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>592689</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7031931</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127484400</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>592527</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7031858</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127480739</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>592672</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7031894</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127482820</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>592658</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7031898</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127481183</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>592727</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7031939</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127481620</v>
+      </c>
+      <c r="B15" t="n">
+        <v>75130</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>308</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>592695</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7031932</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127483297</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>592600</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7031907</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127480832</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>592683</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7031889</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127481178</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>592727</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7031939</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127482577</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78681</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>353</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>592617</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7031890</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127482512</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>592609</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7031869</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127482277</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>592536</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7031910</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127480961</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>592704</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7031881</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127482329</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>592559</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7031898</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127480763</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>592667</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7031888</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127483314</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>592591</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7031906</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127482171</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91900</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>760</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>592610</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7031932</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127481753</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>592670</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7031932</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127480974</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92809</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>592705</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7031887</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127482437</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91291</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>592588</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7031892</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127481075</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>592724</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7031919</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127482031</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>592643</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7031927</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127483311</v>
+      </c>
+      <c r="B32" t="n">
+        <v>88729</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>510</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>592598</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7031904</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127480942</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78772</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>592696</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7031869</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127482952</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>592680</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7031902</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127482742</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>592649</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7031888</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127486071</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91291</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>592561</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7031869</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127483251</v>
+      </c>
+      <c r="B37" t="n">
+        <v>82855</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>592625</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7031937</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127483235</v>
+      </c>
+      <c r="B38" t="n">
+        <v>75138</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>592635</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7031936</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127484950</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91487</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>592522</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7031851</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127481330</v>
+      </c>
+      <c r="B40" t="n">
+        <v>75138</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>592752</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7031965</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127483057</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>592679</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7031907</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127482368</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>592569</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7031901</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127482261</v>
+      </c>
+      <c r="B43" t="n">
+        <v>75130</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>308</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>592559</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7031935</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1390,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127481272</v>
+        <v>127481815</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,39 +1401,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592774</v>
+        <v>592689</v>
       </c>
       <c r="R9" t="n">
-        <v>7031974</v>
+        <v>7031931</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1466,11 +1461,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1497,10 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127481815</v>
+        <v>127481272</v>
       </c>
       <c r="B10" t="n">
-        <v>91326</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1508,34 +1498,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592689</v>
+        <v>592774</v>
       </c>
       <c r="R10" t="n">
-        <v>7031931</v>
+        <v>7031974</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1568,6 +1563,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127480739</v>
+        <v>127482820</v>
       </c>
       <c r="B12" t="n">
-        <v>80117</v>
+        <v>91326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,21 +1702,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592672</v>
+        <v>592658</v>
       </c>
       <c r="R12" t="n">
-        <v>7031894</v>
+        <v>7031898</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127482820</v>
+        <v>127481183</v>
       </c>
       <c r="B13" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592658</v>
+        <v>592727</v>
       </c>
       <c r="R13" t="n">
-        <v>7031898</v>
+        <v>7031939</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127481183</v>
+        <v>127481620</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>75130</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592727</v>
+        <v>592695</v>
       </c>
       <c r="R14" t="n">
-        <v>7031939</v>
+        <v>7031932</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127481620</v>
+        <v>127483297</v>
       </c>
       <c r="B15" t="n">
-        <v>75130</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592695</v>
+        <v>592600</v>
       </c>
       <c r="R15" t="n">
-        <v>7031932</v>
+        <v>7031907</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127483297</v>
+        <v>127480832</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,34 +2090,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592600</v>
+        <v>592683</v>
       </c>
       <c r="R16" t="n">
-        <v>7031907</v>
+        <v>7031889</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2176,10 +2185,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127480832</v>
+        <v>127481178</v>
       </c>
       <c r="B17" t="n">
-        <v>57817</v>
+        <v>57654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,31 +2196,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2220,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592683</v>
+        <v>592727</v>
       </c>
       <c r="R17" t="n">
-        <v>7031889</v>
+        <v>7031939</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2282,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127481178</v>
+        <v>127482577</v>
       </c>
       <c r="B18" t="n">
-        <v>57654</v>
+        <v>78681</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2293,39 +2298,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592727</v>
+        <v>592617</v>
       </c>
       <c r="R18" t="n">
-        <v>7031939</v>
+        <v>7031890</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127482577</v>
+        <v>127482512</v>
       </c>
       <c r="B19" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592617</v>
+        <v>592609</v>
       </c>
       <c r="R19" t="n">
-        <v>7031890</v>
+        <v>7031869</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2481,7 +2481,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127482512</v>
+        <v>127482277</v>
       </c>
       <c r="B20" t="n">
         <v>79014</v>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592609</v>
+        <v>592536</v>
       </c>
       <c r="R20" t="n">
-        <v>7031869</v>
+        <v>7031910</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2578,7 +2578,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127482277</v>
+        <v>127480961</v>
       </c>
       <c r="B21" t="n">
         <v>79014</v>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592536</v>
+        <v>592704</v>
       </c>
       <c r="R21" t="n">
-        <v>7031910</v>
+        <v>7031881</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127480961</v>
+        <v>127482329</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592704</v>
+        <v>592559</v>
       </c>
       <c r="R22" t="n">
-        <v>7031881</v>
+        <v>7031898</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127482329</v>
+        <v>127480763</v>
       </c>
       <c r="B23" t="n">
-        <v>91326</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,21 +2783,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592559</v>
+        <v>592667</v>
       </c>
       <c r="R23" t="n">
-        <v>7031898</v>
+        <v>7031888</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127480763</v>
+        <v>127483314</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2880,21 +2880,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592667</v>
+        <v>592591</v>
       </c>
       <c r="R24" t="n">
-        <v>7031888</v>
+        <v>7031906</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2966,32 +2966,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127483314</v>
+        <v>127482171</v>
       </c>
       <c r="B25" t="n">
-        <v>91326</v>
+        <v>91900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592591</v>
+        <v>592610</v>
       </c>
       <c r="R25" t="n">
-        <v>7031906</v>
+        <v>7031932</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3063,32 +3063,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127482171</v>
+        <v>127481753</v>
       </c>
       <c r="B26" t="n">
-        <v>91900</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592610</v>
+        <v>592670</v>
       </c>
       <c r="R26" t="n">
         <v>7031932</v>
@@ -3160,10 +3160,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127481753</v>
+        <v>127480974</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3171,21 +3171,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592670</v>
+        <v>592705</v>
       </c>
       <c r="R27" t="n">
-        <v>7031932</v>
+        <v>7031887</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127480974</v>
+        <v>127482437</v>
       </c>
       <c r="B28" t="n">
-        <v>92809</v>
+        <v>91291</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592705</v>
+        <v>592588</v>
       </c>
       <c r="R28" t="n">
-        <v>7031887</v>
+        <v>7031892</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3354,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127482437</v>
+        <v>127481075</v>
       </c>
       <c r="B29" t="n">
-        <v>91291</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592588</v>
+        <v>592724</v>
       </c>
       <c r="R29" t="n">
-        <v>7031892</v>
+        <v>7031919</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3451,45 +3451,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127481075</v>
+        <v>127482031</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592724</v>
+        <v>592643</v>
       </c>
       <c r="R30" t="n">
-        <v>7031919</v>
+        <v>7031927</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3548,54 +3557,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127482031</v>
+        <v>127483311</v>
       </c>
       <c r="B31" t="n">
-        <v>98443</v>
+        <v>88729</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592643</v>
+        <v>592598</v>
       </c>
       <c r="R31" t="n">
-        <v>7031927</v>
+        <v>7031904</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127483311</v>
+        <v>127480942</v>
       </c>
       <c r="B32" t="n">
-        <v>88729</v>
+        <v>78772</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,21 +3665,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592598</v>
+        <v>592696</v>
       </c>
       <c r="R32" t="n">
-        <v>7031904</v>
+        <v>7031869</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127480942</v>
+        <v>127482952</v>
       </c>
       <c r="B33" t="n">
-        <v>78772</v>
+        <v>91344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,21 +3762,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592696</v>
+        <v>592680</v>
       </c>
       <c r="R33" t="n">
-        <v>7031869</v>
+        <v>7031902</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3848,10 +3848,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127482952</v>
+        <v>127482742</v>
       </c>
       <c r="B34" t="n">
-        <v>91344</v>
+        <v>57657</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3859,34 +3859,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592680</v>
+        <v>592649</v>
       </c>
       <c r="R34" t="n">
-        <v>7031902</v>
+        <v>7031888</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3919,6 +3924,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3945,50 +3955,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127482742</v>
+        <v>127486071</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>91291</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592649</v>
+        <v>592561</v>
       </c>
       <c r="R35" t="n">
-        <v>7031888</v>
+        <v>7031869</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4021,11 +4026,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4052,32 +4052,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127486071</v>
+        <v>127483251</v>
       </c>
       <c r="B36" t="n">
-        <v>91291</v>
+        <v>82855</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>592561</v>
+        <v>592625</v>
       </c>
       <c r="R36" t="n">
-        <v>7031869</v>
+        <v>7031937</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4149,10 +4149,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127483251</v>
+        <v>127481330</v>
       </c>
       <c r="B37" t="n">
-        <v>82855</v>
+        <v>75138</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4160,21 +4160,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592625</v>
+        <v>592752</v>
       </c>
       <c r="R37" t="n">
-        <v>7031937</v>
+        <v>7031965</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4440,10 +4440,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127481330</v>
+        <v>127483057</v>
       </c>
       <c r="B40" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4451,21 +4451,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592752</v>
+        <v>592679</v>
       </c>
       <c r="R40" t="n">
-        <v>7031965</v>
+        <v>7031907</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4537,7 +4537,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127483057</v>
+        <v>127482368</v>
       </c>
       <c r="B41" t="n">
         <v>79014</v>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592679</v>
+        <v>592569</v>
       </c>
       <c r="R41" t="n">
-        <v>7031907</v>
+        <v>7031901</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4634,10 +4634,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127482368</v>
+        <v>127482261</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>75130</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592569</v>
+        <v>592559</v>
       </c>
       <c r="R42" t="n">
-        <v>7031901</v>
+        <v>7031935</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4728,103 +4728,6 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>127482261</v>
-      </c>
-      <c r="B43" t="n">
-        <v>75130</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>308</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Brunpudrad nållav</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Sjömyran, Sjömyran, Ång</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>592559</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7031935</v>
-      </c>
-      <c r="S43" t="n">
-        <v>15</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Resele</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -995,7 +995,7 @@
         <v>127482681</v>
       </c>
       <c r="B5" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127482288</v>
+        <v>127483367</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,39 +1100,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592543</v>
+        <v>592559</v>
       </c>
       <c r="R6" t="n">
-        <v>7031902</v>
+        <v>7031863</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,11 +1160,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127483367</v>
+        <v>127482288</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1207,34 +1197,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592559</v>
+        <v>592543</v>
       </c>
       <c r="R7" t="n">
-        <v>7031863</v>
+        <v>7031902</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1267,6 +1262,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,7 +1296,7 @@
         <v>127481318</v>
       </c>
       <c r="B8" t="n">
-        <v>75130</v>
+        <v>75134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127481815</v>
+        <v>127484400</v>
       </c>
       <c r="B9" t="n">
-        <v>91326</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,21 +1401,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592689</v>
+        <v>592527</v>
       </c>
       <c r="R9" t="n">
-        <v>7031931</v>
+        <v>7031858</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1490,7 +1490,7 @@
         <v>127481272</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127484400</v>
+        <v>127481815</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>91330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592527</v>
+        <v>592689</v>
       </c>
       <c r="R11" t="n">
-        <v>7031858</v>
+        <v>7031931</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1694,7 +1694,7 @@
         <v>127482820</v>
       </c>
       <c r="B12" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127481183</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127481620</v>
+        <v>127483297</v>
       </c>
       <c r="B14" t="n">
-        <v>75130</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592695</v>
+        <v>592600</v>
       </c>
       <c r="R14" t="n">
-        <v>7031932</v>
+        <v>7031907</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127483297</v>
+        <v>127481620</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>75134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592600</v>
+        <v>592695</v>
       </c>
       <c r="R15" t="n">
-        <v>7031907</v>
+        <v>7031932</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2082,7 +2082,7 @@
         <v>127480832</v>
       </c>
       <c r="B16" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127481178</v>
       </c>
       <c r="B17" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>127482577</v>
       </c>
       <c r="B18" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>127482512</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>127482277</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>127480961</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>127482329</v>
       </c>
       <c r="B22" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>127480763</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127483314</v>
+        <v>127482171</v>
       </c>
       <c r="B24" t="n">
-        <v>91326</v>
+        <v>91904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592591</v>
+        <v>592610</v>
       </c>
       <c r="R24" t="n">
-        <v>7031906</v>
+        <v>7031932</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2966,32 +2966,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127482171</v>
+        <v>127483314</v>
       </c>
       <c r="B25" t="n">
-        <v>91900</v>
+        <v>91330</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592610</v>
+        <v>592591</v>
       </c>
       <c r="R25" t="n">
-        <v>7031932</v>
+        <v>7031906</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3066,7 +3066,7 @@
         <v>127481753</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>127480974</v>
       </c>
       <c r="B27" t="n">
-        <v>92809</v>
+        <v>92813</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>127482437</v>
       </c>
       <c r="B28" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127481075</v>
+        <v>127483311</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>88733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592724</v>
+        <v>592598</v>
       </c>
       <c r="R29" t="n">
-        <v>7031919</v>
+        <v>7031904</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3451,54 +3451,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127482031</v>
+        <v>127481075</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592643</v>
+        <v>592724</v>
       </c>
       <c r="R30" t="n">
-        <v>7031927</v>
+        <v>7031919</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3557,45 +3548,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127483311</v>
+        <v>127482031</v>
       </c>
       <c r="B31" t="n">
-        <v>88729</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592598</v>
+        <v>592643</v>
       </c>
       <c r="R31" t="n">
-        <v>7031904</v>
+        <v>7031927</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127480942</v>
+        <v>127482952</v>
       </c>
       <c r="B32" t="n">
-        <v>78772</v>
+        <v>91348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,21 +3665,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592696</v>
+        <v>592680</v>
       </c>
       <c r="R32" t="n">
-        <v>7031869</v>
+        <v>7031902</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127482952</v>
+        <v>127480942</v>
       </c>
       <c r="B33" t="n">
-        <v>91344</v>
+        <v>78776</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,21 +3762,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592680</v>
+        <v>592696</v>
       </c>
       <c r="R33" t="n">
-        <v>7031902</v>
+        <v>7031869</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3851,7 +3851,7 @@
         <v>127482742</v>
       </c>
       <c r="B34" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>127486071</v>
       </c>
       <c r="B35" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>127483251</v>
       </c>
       <c r="B36" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>127481330</v>
       </c>
       <c r="B37" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>127483235</v>
       </c>
       <c r="B38" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>127484950</v>
       </c>
       <c r="B39" t="n">
-        <v>91487</v>
+        <v>91491</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4440,10 +4440,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127483057</v>
+        <v>127482368</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592679</v>
+        <v>592569</v>
       </c>
       <c r="R40" t="n">
-        <v>7031907</v>
+        <v>7031901</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4537,10 +4537,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127482368</v>
+        <v>127483057</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592569</v>
+        <v>592679</v>
       </c>
       <c r="R41" t="n">
-        <v>7031901</v>
+        <v>7031907</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4637,7 +4637,7 @@
         <v>127482261</v>
       </c>
       <c r="B42" t="n">
-        <v>75130</v>
+        <v>75134</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127482577</v>
+        <v>127482512</v>
       </c>
       <c r="B18" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592617</v>
+        <v>592609</v>
       </c>
       <c r="R18" t="n">
-        <v>7031890</v>
+        <v>7031869</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2384,7 +2384,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127482512</v>
+        <v>127482277</v>
       </c>
       <c r="B19" t="n">
         <v>79018</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592609</v>
+        <v>592536</v>
       </c>
       <c r="R19" t="n">
-        <v>7031869</v>
+        <v>7031910</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127482277</v>
+        <v>127482577</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592536</v>
+        <v>592617</v>
       </c>
       <c r="R20" t="n">
-        <v>7031910</v>
+        <v>7031890</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127482171</v>
+        <v>127481753</v>
       </c>
       <c r="B24" t="n">
-        <v>91904</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592610</v>
+        <v>592670</v>
       </c>
       <c r="R24" t="n">
         <v>7031932</v>
@@ -2966,32 +2966,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127483314</v>
+        <v>127482171</v>
       </c>
       <c r="B25" t="n">
-        <v>91330</v>
+        <v>91904</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592591</v>
+        <v>592610</v>
       </c>
       <c r="R25" t="n">
-        <v>7031906</v>
+        <v>7031932</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3063,10 +3063,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127481753</v>
+        <v>127483314</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3074,21 +3074,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592670</v>
+        <v>592591</v>
       </c>
       <c r="R26" t="n">
-        <v>7031932</v>
+        <v>7031906</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3451,45 +3451,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127481075</v>
+        <v>127482031</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592724</v>
+        <v>592643</v>
       </c>
       <c r="R30" t="n">
-        <v>7031919</v>
+        <v>7031927</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3548,54 +3557,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127482031</v>
+        <v>127481075</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592643</v>
+        <v>592724</v>
       </c>
       <c r="R31" t="n">
-        <v>7031927</v>
+        <v>7031919</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127482952</v>
+        <v>127482742</v>
       </c>
       <c r="B32" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,34 +3665,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592680</v>
+        <v>592649</v>
       </c>
       <c r="R32" t="n">
-        <v>7031902</v>
+        <v>7031888</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3725,6 +3730,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3848,10 +3858,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127482742</v>
+        <v>127482952</v>
       </c>
       <c r="B34" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3859,39 +3869,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592649</v>
+        <v>592680</v>
       </c>
       <c r="R34" t="n">
-        <v>7031888</v>
+        <v>7031902</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3924,11 +3929,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127483367</v>
+        <v>127482288</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,34 +1100,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592559</v>
+        <v>592543</v>
       </c>
       <c r="R6" t="n">
-        <v>7031863</v>
+        <v>7031902</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,6 +1165,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1186,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127482288</v>
+        <v>127483367</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,39 +1207,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592543</v>
+        <v>592559</v>
       </c>
       <c r="R7" t="n">
-        <v>7031902</v>
+        <v>7031863</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1262,11 +1267,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127481272</v>
+        <v>127481815</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,39 +1498,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592774</v>
+        <v>592689</v>
       </c>
       <c r="R10" t="n">
-        <v>7031974</v>
+        <v>7031931</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1563,11 +1558,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1594,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127481815</v>
+        <v>127481272</v>
       </c>
       <c r="B11" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,34 +1595,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592689</v>
+        <v>592774</v>
       </c>
       <c r="R11" t="n">
-        <v>7031931</v>
+        <v>7031974</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1665,6 +1660,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3354,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127483311</v>
+        <v>127481075</v>
       </c>
       <c r="B29" t="n">
-        <v>88733</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592598</v>
+        <v>592724</v>
       </c>
       <c r="R29" t="n">
-        <v>7031904</v>
+        <v>7031919</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3451,54 +3451,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127482031</v>
+        <v>127483311</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>88733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592643</v>
+        <v>592598</v>
       </c>
       <c r="R30" t="n">
-        <v>7031927</v>
+        <v>7031904</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3557,45 +3548,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127481075</v>
+        <v>127482031</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592724</v>
+        <v>592643</v>
       </c>
       <c r="R31" t="n">
-        <v>7031919</v>
+        <v>7031927</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127482742</v>
+        <v>127482952</v>
       </c>
       <c r="B32" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,39 +3665,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592649</v>
+        <v>592680</v>
       </c>
       <c r="R32" t="n">
-        <v>7031888</v>
+        <v>7031902</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3730,11 +3725,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3761,10 +3751,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127480942</v>
+        <v>127482742</v>
       </c>
       <c r="B33" t="n">
-        <v>78776</v>
+        <v>57661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3772,34 +3762,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592696</v>
+        <v>592649</v>
       </c>
       <c r="R33" t="n">
-        <v>7031869</v>
+        <v>7031888</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3832,6 +3827,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3858,10 +3858,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127482952</v>
+        <v>127480942</v>
       </c>
       <c r="B34" t="n">
-        <v>91348</v>
+        <v>78776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3869,21 +3869,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592680</v>
+        <v>592696</v>
       </c>
       <c r="R34" t="n">
-        <v>7031902</v>
+        <v>7031869</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -1487,10 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127481815</v>
+        <v>127481272</v>
       </c>
       <c r="B10" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,34 +1498,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592689</v>
+        <v>592774</v>
       </c>
       <c r="R10" t="n">
-        <v>7031931</v>
+        <v>7031974</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1558,6 +1563,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1584,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127481272</v>
+        <v>127481815</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,39 +1605,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592774</v>
+        <v>592689</v>
       </c>
       <c r="R11" t="n">
-        <v>7031974</v>
+        <v>7031931</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1660,11 +1665,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3354,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127481075</v>
+        <v>127483311</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>88733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592724</v>
+        <v>592598</v>
       </c>
       <c r="R29" t="n">
-        <v>7031919</v>
+        <v>7031904</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3451,45 +3451,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127483311</v>
+        <v>127482031</v>
       </c>
       <c r="B30" t="n">
-        <v>88733</v>
+        <v>98447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592598</v>
+        <v>592643</v>
       </c>
       <c r="R30" t="n">
-        <v>7031904</v>
+        <v>7031927</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3548,54 +3557,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127482031</v>
+        <v>127481075</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592643</v>
+        <v>592724</v>
       </c>
       <c r="R31" t="n">
-        <v>7031927</v>
+        <v>7031919</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4149,32 +4149,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127481330</v>
+        <v>127484950</v>
       </c>
       <c r="B37" t="n">
-        <v>75142</v>
+        <v>91491</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592752</v>
+        <v>592522</v>
       </c>
       <c r="R37" t="n">
-        <v>7031965</v>
+        <v>7031851</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4246,7 +4246,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127483235</v>
+        <v>127481330</v>
       </c>
       <c r="B38" t="n">
         <v>75142</v>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592635</v>
+        <v>592752</v>
       </c>
       <c r="R38" t="n">
-        <v>7031936</v>
+        <v>7031965</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4343,32 +4343,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127484950</v>
+        <v>127483235</v>
       </c>
       <c r="B39" t="n">
-        <v>91491</v>
+        <v>75142</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592522</v>
+        <v>592635</v>
       </c>
       <c r="R39" t="n">
-        <v>7031851</v>
+        <v>7031936</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127482288</v>
+        <v>127483367</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,39 +1100,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592543</v>
+        <v>592559</v>
       </c>
       <c r="R6" t="n">
-        <v>7031902</v>
+        <v>7031863</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,11 +1160,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127483367</v>
+        <v>127482288</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1207,34 +1197,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592559</v>
+        <v>592543</v>
       </c>
       <c r="R7" t="n">
-        <v>7031863</v>
+        <v>7031902</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1267,6 +1262,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127484400</v>
+        <v>127481815</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,21 +1401,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592527</v>
+        <v>592689</v>
       </c>
       <c r="R9" t="n">
-        <v>7031858</v>
+        <v>7031931</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1594,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127481815</v>
+        <v>127484400</v>
       </c>
       <c r="B11" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,21 +1605,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592689</v>
+        <v>592527</v>
       </c>
       <c r="R11" t="n">
-        <v>7031931</v>
+        <v>7031858</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127481753</v>
+        <v>127483314</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2880,21 +2880,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592670</v>
+        <v>592591</v>
       </c>
       <c r="R24" t="n">
-        <v>7031932</v>
+        <v>7031906</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2966,32 +2966,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127482171</v>
+        <v>127481753</v>
       </c>
       <c r="B25" t="n">
-        <v>91904</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592610</v>
+        <v>592670</v>
       </c>
       <c r="R25" t="n">
         <v>7031932</v>
@@ -3063,32 +3063,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127483314</v>
+        <v>127482171</v>
       </c>
       <c r="B26" t="n">
-        <v>91330</v>
+        <v>91904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592591</v>
+        <v>592610</v>
       </c>
       <c r="R26" t="n">
-        <v>7031906</v>
+        <v>7031932</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3160,32 +3160,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127480974</v>
+        <v>127482437</v>
       </c>
       <c r="B27" t="n">
-        <v>92813</v>
+        <v>91295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592705</v>
+        <v>592588</v>
       </c>
       <c r="R27" t="n">
-        <v>7031887</v>
+        <v>7031892</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127482437</v>
+        <v>127480974</v>
       </c>
       <c r="B28" t="n">
-        <v>91295</v>
+        <v>92813</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592588</v>
+        <v>592705</v>
       </c>
       <c r="R28" t="n">
-        <v>7031892</v>
+        <v>7031887</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3451,54 +3451,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127482031</v>
+        <v>127481075</v>
       </c>
       <c r="B30" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592643</v>
+        <v>592724</v>
       </c>
       <c r="R30" t="n">
-        <v>7031927</v>
+        <v>7031919</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3557,45 +3548,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127481075</v>
+        <v>127482031</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592724</v>
+        <v>592643</v>
       </c>
       <c r="R31" t="n">
-        <v>7031919</v>
+        <v>7031927</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127482742</v>
+        <v>127480942</v>
       </c>
       <c r="B33" t="n">
-        <v>57661</v>
+        <v>78776</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,39 +3762,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592649</v>
+        <v>592696</v>
       </c>
       <c r="R33" t="n">
-        <v>7031888</v>
+        <v>7031869</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3827,11 +3822,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3858,10 +3848,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127480942</v>
+        <v>127482742</v>
       </c>
       <c r="B34" t="n">
-        <v>78776</v>
+        <v>57661</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3869,34 +3859,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592696</v>
+        <v>592649</v>
       </c>
       <c r="R34" t="n">
-        <v>7031869</v>
+        <v>7031888</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3929,6 +3924,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4246,7 +4246,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127481330</v>
+        <v>127483235</v>
       </c>
       <c r="B38" t="n">
         <v>75142</v>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592752</v>
+        <v>592635</v>
       </c>
       <c r="R38" t="n">
-        <v>7031965</v>
+        <v>7031936</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127483235</v>
+        <v>127481330</v>
       </c>
       <c r="B39" t="n">
         <v>75142</v>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592635</v>
+        <v>592752</v>
       </c>
       <c r="R39" t="n">
-        <v>7031936</v>
+        <v>7031965</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127480961</v>
+        <v>127482329</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592704</v>
+        <v>592559</v>
       </c>
       <c r="R21" t="n">
-        <v>7031881</v>
+        <v>7031898</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127482329</v>
+        <v>127480961</v>
       </c>
       <c r="B22" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592559</v>
+        <v>592704</v>
       </c>
       <c r="R22" t="n">
-        <v>7031898</v>
+        <v>7031881</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127483314</v>
+        <v>127482171</v>
       </c>
       <c r="B24" t="n">
-        <v>91330</v>
+        <v>91904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592591</v>
+        <v>592610</v>
       </c>
       <c r="R24" t="n">
-        <v>7031906</v>
+        <v>7031932</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2966,10 +2966,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127481753</v>
+        <v>127483314</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2977,21 +2977,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592670</v>
+        <v>592591</v>
       </c>
       <c r="R25" t="n">
-        <v>7031932</v>
+        <v>7031906</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3063,32 +3063,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127482171</v>
+        <v>127481753</v>
       </c>
       <c r="B26" t="n">
-        <v>91904</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592610</v>
+        <v>592670</v>
       </c>
       <c r="R26" t="n">
         <v>7031932</v>
@@ -3160,32 +3160,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127482437</v>
+        <v>127480974</v>
       </c>
       <c r="B27" t="n">
-        <v>91295</v>
+        <v>92813</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592588</v>
+        <v>592705</v>
       </c>
       <c r="R27" t="n">
-        <v>7031892</v>
+        <v>7031887</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127480974</v>
+        <v>127482437</v>
       </c>
       <c r="B28" t="n">
-        <v>92813</v>
+        <v>91295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592705</v>
+        <v>592588</v>
       </c>
       <c r="R28" t="n">
-        <v>7031887</v>
+        <v>7031892</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127482952</v>
+        <v>127482742</v>
       </c>
       <c r="B32" t="n">
-        <v>91348</v>
+        <v>57661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,34 +3665,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592680</v>
+        <v>592649</v>
       </c>
       <c r="R32" t="n">
-        <v>7031902</v>
+        <v>7031888</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3725,6 +3730,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3751,10 +3761,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127480942</v>
+        <v>127482952</v>
       </c>
       <c r="B33" t="n">
-        <v>78776</v>
+        <v>91348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,21 +3772,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3786,10 +3796,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592696</v>
+        <v>592680</v>
       </c>
       <c r="R33" t="n">
-        <v>7031869</v>
+        <v>7031902</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3848,10 +3858,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127482742</v>
+        <v>127480942</v>
       </c>
       <c r="B34" t="n">
-        <v>57661</v>
+        <v>78776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3859,39 +3869,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592649</v>
+        <v>592696</v>
       </c>
       <c r="R34" t="n">
-        <v>7031888</v>
+        <v>7031869</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3924,11 +3929,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -995,7 +995,7 @@
         <v>127482681</v>
       </c>
       <c r="B5" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>127483367</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>127482288</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>127481318</v>
       </c>
       <c r="B8" t="n">
-        <v>75134</v>
+        <v>75136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127481815</v>
+        <v>127484400</v>
       </c>
       <c r="B9" t="n">
-        <v>91330</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,21 +1401,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592689</v>
+        <v>592527</v>
       </c>
       <c r="R9" t="n">
-        <v>7031931</v>
+        <v>7031858</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127481272</v>
+        <v>127481815</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>91332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,39 +1498,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592774</v>
+        <v>592689</v>
       </c>
       <c r="R10" t="n">
-        <v>7031974</v>
+        <v>7031931</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1563,11 +1558,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1594,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127484400</v>
+        <v>127481272</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,34 +1595,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592527</v>
+        <v>592774</v>
       </c>
       <c r="R11" t="n">
-        <v>7031858</v>
+        <v>7031974</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1665,6 +1660,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,7 +1694,7 @@
         <v>127482820</v>
       </c>
       <c r="B12" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127481183</v>
+        <v>127481620</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>75136</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592727</v>
+        <v>592695</v>
       </c>
       <c r="R13" t="n">
-        <v>7031939</v>
+        <v>7031932</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127483297</v>
+        <v>127481183</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592600</v>
+        <v>592727</v>
       </c>
       <c r="R14" t="n">
-        <v>7031907</v>
+        <v>7031939</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127481620</v>
+        <v>127483297</v>
       </c>
       <c r="B15" t="n">
-        <v>75134</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592695</v>
+        <v>592600</v>
       </c>
       <c r="R15" t="n">
-        <v>7031932</v>
+        <v>7031907</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2082,7 +2082,7 @@
         <v>127480832</v>
       </c>
       <c r="B16" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127481178</v>
       </c>
       <c r="B17" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127482512</v>
+        <v>127482577</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>78687</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592609</v>
+        <v>592617</v>
       </c>
       <c r="R18" t="n">
-        <v>7031869</v>
+        <v>7031890</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127482277</v>
+        <v>127482512</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592536</v>
+        <v>592609</v>
       </c>
       <c r="R19" t="n">
-        <v>7031910</v>
+        <v>7031869</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127482577</v>
+        <v>127482277</v>
       </c>
       <c r="B20" t="n">
-        <v>78685</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592617</v>
+        <v>592536</v>
       </c>
       <c r="R20" t="n">
-        <v>7031890</v>
+        <v>7031910</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2581,7 +2581,7 @@
         <v>127482329</v>
       </c>
       <c r="B21" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>127480961</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>127480763</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>127482171</v>
       </c>
       <c r="B24" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>127483314</v>
       </c>
       <c r="B25" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>127481753</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>127480974</v>
       </c>
       <c r="B27" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>127482437</v>
       </c>
       <c r="B28" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127483311</v>
+        <v>127481075</v>
       </c>
       <c r="B29" t="n">
-        <v>88733</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592598</v>
+        <v>592724</v>
       </c>
       <c r="R29" t="n">
-        <v>7031904</v>
+        <v>7031919</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3451,45 +3451,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127481075</v>
+        <v>127482031</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592724</v>
+        <v>592643</v>
       </c>
       <c r="R30" t="n">
-        <v>7031919</v>
+        <v>7031927</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3548,54 +3557,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127482031</v>
+        <v>127483311</v>
       </c>
       <c r="B31" t="n">
-        <v>98448</v>
+        <v>88735</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592643</v>
+        <v>592598</v>
       </c>
       <c r="R31" t="n">
-        <v>7031927</v>
+        <v>7031904</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3657,7 +3657,7 @@
         <v>127482742</v>
       </c>
       <c r="B32" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>127482952</v>
       </c>
       <c r="B33" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>127480942</v>
       </c>
       <c r="B34" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>127486071</v>
       </c>
       <c r="B35" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>127483251</v>
       </c>
       <c r="B36" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>127484950</v>
       </c>
       <c r="B37" t="n">
-        <v>91491</v>
+        <v>91493</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4246,10 +4246,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127483235</v>
+        <v>127481330</v>
       </c>
       <c r="B38" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592635</v>
+        <v>592752</v>
       </c>
       <c r="R38" t="n">
-        <v>7031936</v>
+        <v>7031965</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127481330</v>
+        <v>127483235</v>
       </c>
       <c r="B39" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592752</v>
+        <v>592635</v>
       </c>
       <c r="R39" t="n">
-        <v>7031965</v>
+        <v>7031936</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4440,10 +4440,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127482368</v>
+        <v>127482261</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>75136</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4451,21 +4451,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592569</v>
+        <v>592559</v>
       </c>
       <c r="R40" t="n">
-        <v>7031901</v>
+        <v>7031935</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4537,10 +4537,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127483057</v>
+        <v>127482368</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592679</v>
+        <v>592569</v>
       </c>
       <c r="R41" t="n">
-        <v>7031907</v>
+        <v>7031901</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4634,10 +4634,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127482261</v>
+        <v>127483057</v>
       </c>
       <c r="B42" t="n">
-        <v>75134</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592559</v>
+        <v>592679</v>
       </c>
       <c r="R42" t="n">
-        <v>7031935</v>
+        <v>7031907</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -2384,7 +2384,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127482512</v>
+        <v>127482277</v>
       </c>
       <c r="B19" t="n">
         <v>79020</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592609</v>
+        <v>592536</v>
       </c>
       <c r="R19" t="n">
-        <v>7031869</v>
+        <v>7031910</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2481,7 +2481,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127482277</v>
+        <v>127482512</v>
       </c>
       <c r="B20" t="n">
         <v>79020</v>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592536</v>
+        <v>592609</v>
       </c>
       <c r="R20" t="n">
-        <v>7031910</v>
+        <v>7031869</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127482329</v>
+        <v>127480961</v>
       </c>
       <c r="B21" t="n">
-        <v>91332</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592559</v>
+        <v>592704</v>
       </c>
       <c r="R21" t="n">
-        <v>7031898</v>
+        <v>7031881</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127480961</v>
+        <v>127482329</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592704</v>
+        <v>592559</v>
       </c>
       <c r="R22" t="n">
-        <v>7031881</v>
+        <v>7031898</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127482171</v>
+        <v>127481753</v>
       </c>
       <c r="B24" t="n">
-        <v>91906</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592610</v>
+        <v>592670</v>
       </c>
       <c r="R24" t="n">
         <v>7031932</v>
@@ -2966,32 +2966,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127483314</v>
+        <v>127482171</v>
       </c>
       <c r="B25" t="n">
-        <v>91332</v>
+        <v>91906</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592591</v>
+        <v>592610</v>
       </c>
       <c r="R25" t="n">
-        <v>7031906</v>
+        <v>7031932</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3063,10 +3063,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127481753</v>
+        <v>127483314</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>91332</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3074,21 +3074,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592670</v>
+        <v>592591</v>
       </c>
       <c r="R26" t="n">
-        <v>7031932</v>
+        <v>7031906</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127481075</v>
+        <v>127483311</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>88735</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592724</v>
+        <v>592598</v>
       </c>
       <c r="R29" t="n">
-        <v>7031919</v>
+        <v>7031904</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3557,10 +3557,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127483311</v>
+        <v>127481075</v>
       </c>
       <c r="B31" t="n">
-        <v>88735</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3568,21 +3568,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592598</v>
+        <v>592724</v>
       </c>
       <c r="R31" t="n">
-        <v>7031904</v>
+        <v>7031919</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127482742</v>
+        <v>127482952</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,39 +3665,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592649</v>
+        <v>592680</v>
       </c>
       <c r="R32" t="n">
-        <v>7031888</v>
+        <v>7031902</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3730,11 +3725,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3761,10 +3751,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127482952</v>
+        <v>127482742</v>
       </c>
       <c r="B33" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3772,34 +3762,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592680</v>
+        <v>592649</v>
       </c>
       <c r="R33" t="n">
-        <v>7031902</v>
+        <v>7031888</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3832,6 +3827,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4440,10 +4440,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127482261</v>
+        <v>127483057</v>
       </c>
       <c r="B40" t="n">
-        <v>75136</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4451,21 +4451,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592559</v>
+        <v>592679</v>
       </c>
       <c r="R40" t="n">
-        <v>7031935</v>
+        <v>7031907</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4634,10 +4634,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127483057</v>
+        <v>127482261</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>75136</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592679</v>
+        <v>592559</v>
       </c>
       <c r="R42" t="n">
-        <v>7031907</v>
+        <v>7031935</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -3751,10 +3751,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127482742</v>
+        <v>127480942</v>
       </c>
       <c r="B33" t="n">
-        <v>57663</v>
+        <v>78778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,39 +3762,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592649</v>
+        <v>592696</v>
       </c>
       <c r="R33" t="n">
-        <v>7031888</v>
+        <v>7031869</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3827,11 +3822,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3858,10 +3848,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127480942</v>
+        <v>127482742</v>
       </c>
       <c r="B34" t="n">
-        <v>78778</v>
+        <v>57663</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3869,34 +3859,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592696</v>
+        <v>592649</v>
       </c>
       <c r="R34" t="n">
-        <v>7031869</v>
+        <v>7031888</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3929,6 +3924,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127481620</v>
+        <v>127481183</v>
       </c>
       <c r="B13" t="n">
-        <v>75136</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592695</v>
+        <v>592727</v>
       </c>
       <c r="R13" t="n">
-        <v>7031932</v>
+        <v>7031939</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127481183</v>
+        <v>127483297</v>
       </c>
       <c r="B14" t="n">
         <v>79020</v>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592727</v>
+        <v>592600</v>
       </c>
       <c r="R14" t="n">
-        <v>7031939</v>
+        <v>7031907</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127483297</v>
+        <v>127481620</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>75136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592600</v>
+        <v>592695</v>
       </c>
       <c r="R15" t="n">
-        <v>7031907</v>
+        <v>7031932</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2384,7 +2384,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127482277</v>
+        <v>127482512</v>
       </c>
       <c r="B19" t="n">
         <v>79020</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592536</v>
+        <v>592609</v>
       </c>
       <c r="R19" t="n">
-        <v>7031910</v>
+        <v>7031869</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2481,7 +2481,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127482512</v>
+        <v>127482277</v>
       </c>
       <c r="B20" t="n">
         <v>79020</v>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592609</v>
+        <v>592536</v>
       </c>
       <c r="R20" t="n">
-        <v>7031869</v>
+        <v>7031910</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3160,32 +3160,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127480974</v>
+        <v>127482437</v>
       </c>
       <c r="B27" t="n">
-        <v>92815</v>
+        <v>91297</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592705</v>
+        <v>592588</v>
       </c>
       <c r="R27" t="n">
-        <v>7031887</v>
+        <v>7031892</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127482437</v>
+        <v>127480974</v>
       </c>
       <c r="B28" t="n">
-        <v>91297</v>
+        <v>92815</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592588</v>
+        <v>592705</v>
       </c>
       <c r="R28" t="n">
-        <v>7031892</v>
+        <v>7031887</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127483311</v>
+        <v>127481075</v>
       </c>
       <c r="B29" t="n">
-        <v>88735</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592598</v>
+        <v>592724</v>
       </c>
       <c r="R29" t="n">
-        <v>7031904</v>
+        <v>7031919</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3557,10 +3557,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127481075</v>
+        <v>127483311</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>88735</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3568,21 +3568,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592724</v>
+        <v>592598</v>
       </c>
       <c r="R31" t="n">
-        <v>7031919</v>
+        <v>7031904</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127482952</v>
+        <v>127480942</v>
       </c>
       <c r="B32" t="n">
-        <v>91350</v>
+        <v>78778</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,21 +3665,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592680</v>
+        <v>592696</v>
       </c>
       <c r="R32" t="n">
-        <v>7031902</v>
+        <v>7031869</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127480942</v>
+        <v>127482952</v>
       </c>
       <c r="B33" t="n">
-        <v>78778</v>
+        <v>91350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,21 +3762,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592696</v>
+        <v>592680</v>
       </c>
       <c r="R33" t="n">
-        <v>7031869</v>
+        <v>7031902</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4149,32 +4149,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127484950</v>
+        <v>127481330</v>
       </c>
       <c r="B37" t="n">
-        <v>91493</v>
+        <v>75144</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592522</v>
+        <v>592752</v>
       </c>
       <c r="R37" t="n">
-        <v>7031851</v>
+        <v>7031965</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4246,7 +4246,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127481330</v>
+        <v>127483235</v>
       </c>
       <c r="B38" t="n">
         <v>75144</v>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592752</v>
+        <v>592635</v>
       </c>
       <c r="R38" t="n">
-        <v>7031965</v>
+        <v>7031936</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4343,32 +4343,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127483235</v>
+        <v>127484950</v>
       </c>
       <c r="B39" t="n">
-        <v>75144</v>
+        <v>91493</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592635</v>
+        <v>592522</v>
       </c>
       <c r="R39" t="n">
-        <v>7031936</v>
+        <v>7031851</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4440,7 +4440,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127483057</v>
+        <v>127482368</v>
       </c>
       <c r="B40" t="n">
         <v>79020</v>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592679</v>
+        <v>592569</v>
       </c>
       <c r="R40" t="n">
-        <v>7031907</v>
+        <v>7031901</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4537,7 +4537,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127482368</v>
+        <v>127483057</v>
       </c>
       <c r="B41" t="n">
         <v>79020</v>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592569</v>
+        <v>592679</v>
       </c>
       <c r="R41" t="n">
-        <v>7031901</v>
+        <v>7031907</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -1490,7 +1490,7 @@
         <v>127481815</v>
       </c>
       <c r="B10" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>127482820</v>
       </c>
       <c r="B12" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127481183</v>
+        <v>127483297</v>
       </c>
       <c r="B13" t="n">
         <v>79020</v>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592727</v>
+        <v>592600</v>
       </c>
       <c r="R13" t="n">
-        <v>7031939</v>
+        <v>7031907</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127483297</v>
+        <v>127481620</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>75136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592600</v>
+        <v>592695</v>
       </c>
       <c r="R14" t="n">
-        <v>7031907</v>
+        <v>7031932</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127481620</v>
+        <v>127481183</v>
       </c>
       <c r="B15" t="n">
-        <v>75136</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592695</v>
+        <v>592727</v>
       </c>
       <c r="R15" t="n">
-        <v>7031932</v>
+        <v>7031939</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127482577</v>
+        <v>127482512</v>
       </c>
       <c r="B18" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592617</v>
+        <v>592609</v>
       </c>
       <c r="R18" t="n">
-        <v>7031890</v>
+        <v>7031869</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2384,7 +2384,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127482512</v>
+        <v>127482277</v>
       </c>
       <c r="B19" t="n">
         <v>79020</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592609</v>
+        <v>592536</v>
       </c>
       <c r="R19" t="n">
-        <v>7031869</v>
+        <v>7031910</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127482277</v>
+        <v>127482577</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592536</v>
+        <v>592617</v>
       </c>
       <c r="R20" t="n">
-        <v>7031910</v>
+        <v>7031890</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2678,7 +2678,7 @@
         <v>127482329</v>
       </c>
       <c r="B22" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127481753</v>
+        <v>127482171</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>91912</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592670</v>
+        <v>592610</v>
       </c>
       <c r="R24" t="n">
         <v>7031932</v>
@@ -2966,32 +2966,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127482171</v>
+        <v>127483314</v>
       </c>
       <c r="B25" t="n">
-        <v>91906</v>
+        <v>91338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592610</v>
+        <v>592591</v>
       </c>
       <c r="R25" t="n">
-        <v>7031932</v>
+        <v>7031906</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3063,10 +3063,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127483314</v>
+        <v>127481753</v>
       </c>
       <c r="B26" t="n">
-        <v>91332</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3074,21 +3074,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592591</v>
+        <v>592670</v>
       </c>
       <c r="R26" t="n">
-        <v>7031906</v>
+        <v>7031932</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3160,32 +3160,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127482437</v>
+        <v>127480974</v>
       </c>
       <c r="B27" t="n">
-        <v>91297</v>
+        <v>92821</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592588</v>
+        <v>592705</v>
       </c>
       <c r="R27" t="n">
-        <v>7031892</v>
+        <v>7031887</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127480974</v>
+        <v>127482437</v>
       </c>
       <c r="B28" t="n">
-        <v>92815</v>
+        <v>91303</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592705</v>
+        <v>592588</v>
       </c>
       <c r="R28" t="n">
-        <v>7031887</v>
+        <v>7031892</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3451,54 +3451,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127482031</v>
+        <v>127483311</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>88741</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592643</v>
+        <v>592598</v>
       </c>
       <c r="R30" t="n">
-        <v>7031927</v>
+        <v>7031904</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3557,45 +3548,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127483311</v>
+        <v>127482031</v>
       </c>
       <c r="B31" t="n">
-        <v>88735</v>
+        <v>98456</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592598</v>
+        <v>592643</v>
       </c>
       <c r="R31" t="n">
-        <v>7031904</v>
+        <v>7031927</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127482952</v>
+        <v>127482742</v>
       </c>
       <c r="B33" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,34 +3762,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592680</v>
+        <v>592649</v>
       </c>
       <c r="R33" t="n">
-        <v>7031902</v>
+        <v>7031888</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3822,6 +3827,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3848,10 +3858,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127482742</v>
+        <v>127482952</v>
       </c>
       <c r="B34" t="n">
-        <v>57663</v>
+        <v>91356</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3859,39 +3869,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592649</v>
+        <v>592680</v>
       </c>
       <c r="R34" t="n">
-        <v>7031888</v>
+        <v>7031902</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3924,11 +3929,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3958,7 +3958,7 @@
         <v>127486071</v>
       </c>
       <c r="B35" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4246,32 +4246,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127483235</v>
+        <v>127484950</v>
       </c>
       <c r="B38" t="n">
-        <v>75144</v>
+        <v>91499</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592635</v>
+        <v>592522</v>
       </c>
       <c r="R38" t="n">
-        <v>7031936</v>
+        <v>7031851</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4343,32 +4343,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127484950</v>
+        <v>127483235</v>
       </c>
       <c r="B39" t="n">
-        <v>91493</v>
+        <v>75144</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592522</v>
+        <v>592635</v>
       </c>
       <c r="R39" t="n">
-        <v>7031851</v>
+        <v>7031936</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4440,10 +4440,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127482368</v>
+        <v>127482261</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>75136</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4451,21 +4451,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592569</v>
+        <v>592559</v>
       </c>
       <c r="R40" t="n">
-        <v>7031901</v>
+        <v>7031935</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4537,7 +4537,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127483057</v>
+        <v>127482368</v>
       </c>
       <c r="B41" t="n">
         <v>79020</v>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592679</v>
+        <v>592569</v>
       </c>
       <c r="R41" t="n">
-        <v>7031907</v>
+        <v>7031901</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4634,10 +4634,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127482261</v>
+        <v>127483057</v>
       </c>
       <c r="B42" t="n">
-        <v>75136</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592559</v>
+        <v>592679</v>
       </c>
       <c r="R42" t="n">
-        <v>7031935</v>
+        <v>7031907</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -995,7 +995,7 @@
         <v>127482681</v>
       </c>
       <c r="B5" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>127483367</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>127482288</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>127481318</v>
       </c>
       <c r="B8" t="n">
-        <v>75136</v>
+        <v>75139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127484400</v>
+        <v>127481815</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>91341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,21 +1401,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592527</v>
+        <v>592689</v>
       </c>
       <c r="R9" t="n">
-        <v>7031858</v>
+        <v>7031931</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127481815</v>
+        <v>127484400</v>
       </c>
       <c r="B10" t="n">
-        <v>91338</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,21 +1498,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592689</v>
+        <v>592527</v>
       </c>
       <c r="R10" t="n">
-        <v>7031931</v>
+        <v>7031858</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1587,7 +1587,7 @@
         <v>127481272</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>127482820</v>
       </c>
       <c r="B12" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127483297</v>
+        <v>127481183</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592600</v>
+        <v>592727</v>
       </c>
       <c r="R13" t="n">
-        <v>7031907</v>
+        <v>7031939</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127481620</v>
+        <v>127483297</v>
       </c>
       <c r="B14" t="n">
-        <v>75136</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,21 +1896,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592695</v>
+        <v>592600</v>
       </c>
       <c r="R14" t="n">
-        <v>7031932</v>
+        <v>7031907</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127481183</v>
+        <v>127481620</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>75139</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592727</v>
+        <v>592695</v>
       </c>
       <c r="R15" t="n">
-        <v>7031939</v>
+        <v>7031932</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2082,7 +2082,7 @@
         <v>127480832</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127481178</v>
       </c>
       <c r="B17" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127482512</v>
+        <v>127482577</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>78690</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592609</v>
+        <v>592617</v>
       </c>
       <c r="R18" t="n">
-        <v>7031869</v>
+        <v>7031890</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127482277</v>
+        <v>127482512</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592536</v>
+        <v>592609</v>
       </c>
       <c r="R19" t="n">
-        <v>7031910</v>
+        <v>7031869</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127482577</v>
+        <v>127482277</v>
       </c>
       <c r="B20" t="n">
-        <v>78687</v>
+        <v>79023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592617</v>
+        <v>592536</v>
       </c>
       <c r="R20" t="n">
-        <v>7031890</v>
+        <v>7031910</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127480961</v>
+        <v>127482329</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>91341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592704</v>
+        <v>592559</v>
       </c>
       <c r="R21" t="n">
-        <v>7031881</v>
+        <v>7031898</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127482329</v>
+        <v>127480961</v>
       </c>
       <c r="B22" t="n">
-        <v>91338</v>
+        <v>79023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592559</v>
+        <v>592704</v>
       </c>
       <c r="R22" t="n">
-        <v>7031898</v>
+        <v>7031881</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2775,7 +2775,7 @@
         <v>127480763</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>127482171</v>
       </c>
       <c r="B24" t="n">
-        <v>91912</v>
+        <v>91915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>127483314</v>
       </c>
       <c r="B25" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>127481753</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>127480974</v>
       </c>
       <c r="B27" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>127482437</v>
       </c>
       <c r="B28" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127481075</v>
+        <v>127483311</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>88744</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592724</v>
+        <v>592598</v>
       </c>
       <c r="R29" t="n">
-        <v>7031919</v>
+        <v>7031904</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3451,45 +3451,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127483311</v>
+        <v>127482031</v>
       </c>
       <c r="B30" t="n">
-        <v>88741</v>
+        <v>98459</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592598</v>
+        <v>592643</v>
       </c>
       <c r="R30" t="n">
-        <v>7031904</v>
+        <v>7031927</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3548,54 +3557,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127482031</v>
+        <v>127481075</v>
       </c>
       <c r="B31" t="n">
-        <v>98456</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592643</v>
+        <v>592724</v>
       </c>
       <c r="R31" t="n">
-        <v>7031927</v>
+        <v>7031919</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3657,7 +3657,7 @@
         <v>127480942</v>
       </c>
       <c r="B32" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>127482742</v>
       </c>
       <c r="B33" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>127482952</v>
       </c>
       <c r="B34" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>127486071</v>
       </c>
       <c r="B35" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>127483251</v>
       </c>
       <c r="B36" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4149,32 +4149,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127481330</v>
+        <v>127484950</v>
       </c>
       <c r="B37" t="n">
-        <v>75144</v>
+        <v>91502</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592752</v>
+        <v>592522</v>
       </c>
       <c r="R37" t="n">
-        <v>7031965</v>
+        <v>7031851</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4246,32 +4246,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127484950</v>
+        <v>127481330</v>
       </c>
       <c r="B38" t="n">
-        <v>91499</v>
+        <v>75147</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592522</v>
+        <v>592752</v>
       </c>
       <c r="R38" t="n">
-        <v>7031851</v>
+        <v>7031965</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4346,7 +4346,7 @@
         <v>127483235</v>
       </c>
       <c r="B39" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4440,10 +4440,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127482261</v>
+        <v>127482368</v>
       </c>
       <c r="B40" t="n">
-        <v>75136</v>
+        <v>79023</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4451,21 +4451,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592559</v>
+        <v>592569</v>
       </c>
       <c r="R40" t="n">
-        <v>7031935</v>
+        <v>7031901</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4537,10 +4537,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127482368</v>
+        <v>127482261</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>75139</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4548,21 +4548,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592569</v>
+        <v>592559</v>
       </c>
       <c r="R41" t="n">
-        <v>7031901</v>
+        <v>7031935</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4637,7 +4637,7 @@
         <v>127483057</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -995,7 +995,7 @@
         <v>127482681</v>
       </c>
       <c r="B5" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>127483367</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>127482288</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>127481318</v>
       </c>
       <c r="B8" t="n">
-        <v>75139</v>
+        <v>75145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>127481815</v>
       </c>
       <c r="B9" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>127484400</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127481272</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>127482820</v>
       </c>
       <c r="B12" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127481183</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>127483297</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>127481620</v>
       </c>
       <c r="B15" t="n">
-        <v>75139</v>
+        <v>75145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>127480832</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>127481178</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127482577</v>
+        <v>127482512</v>
       </c>
       <c r="B18" t="n">
-        <v>78690</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592617</v>
+        <v>592609</v>
       </c>
       <c r="R18" t="n">
-        <v>7031890</v>
+        <v>7031869</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127482512</v>
+        <v>127482277</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592609</v>
+        <v>592536</v>
       </c>
       <c r="R19" t="n">
-        <v>7031869</v>
+        <v>7031910</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127482277</v>
+        <v>127482577</v>
       </c>
       <c r="B20" t="n">
-        <v>79023</v>
+        <v>78696</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592536</v>
+        <v>592617</v>
       </c>
       <c r="R20" t="n">
-        <v>7031910</v>
+        <v>7031890</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127482329</v>
+        <v>127480961</v>
       </c>
       <c r="B21" t="n">
-        <v>91341</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592559</v>
+        <v>592704</v>
       </c>
       <c r="R21" t="n">
-        <v>7031898</v>
+        <v>7031881</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127480961</v>
+        <v>127482329</v>
       </c>
       <c r="B22" t="n">
-        <v>79023</v>
+        <v>91349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592704</v>
+        <v>592559</v>
       </c>
       <c r="R22" t="n">
-        <v>7031881</v>
+        <v>7031898</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2775,7 +2775,7 @@
         <v>127480763</v>
       </c>
       <c r="B23" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127482171</v>
+        <v>127481753</v>
       </c>
       <c r="B24" t="n">
-        <v>91915</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592610</v>
+        <v>592670</v>
       </c>
       <c r="R24" t="n">
         <v>7031932</v>
@@ -2966,32 +2966,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127483314</v>
+        <v>127482171</v>
       </c>
       <c r="B25" t="n">
-        <v>91341</v>
+        <v>91923</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592591</v>
+        <v>592610</v>
       </c>
       <c r="R25" t="n">
-        <v>7031906</v>
+        <v>7031932</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3063,10 +3063,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127481753</v>
+        <v>127483314</v>
       </c>
       <c r="B26" t="n">
-        <v>79023</v>
+        <v>91349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3074,21 +3074,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592670</v>
+        <v>592591</v>
       </c>
       <c r="R26" t="n">
-        <v>7031932</v>
+        <v>7031906</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3160,32 +3160,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127480974</v>
+        <v>127482437</v>
       </c>
       <c r="B27" t="n">
-        <v>92824</v>
+        <v>91314</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592705</v>
+        <v>592588</v>
       </c>
       <c r="R27" t="n">
-        <v>7031887</v>
+        <v>7031892</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127482437</v>
+        <v>127480974</v>
       </c>
       <c r="B28" t="n">
-        <v>91306</v>
+        <v>92832</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592588</v>
+        <v>592705</v>
       </c>
       <c r="R28" t="n">
-        <v>7031892</v>
+        <v>7031887</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127483311</v>
+        <v>127481075</v>
       </c>
       <c r="B29" t="n">
-        <v>88744</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592598</v>
+        <v>592724</v>
       </c>
       <c r="R29" t="n">
-        <v>7031904</v>
+        <v>7031919</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3454,7 +3454,7 @@
         <v>127482031</v>
       </c>
       <c r="B30" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3557,10 +3557,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127481075</v>
+        <v>127483311</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>88752</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3568,21 +3568,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592724</v>
+        <v>592598</v>
       </c>
       <c r="R31" t="n">
-        <v>7031919</v>
+        <v>7031904</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127480942</v>
+        <v>127482952</v>
       </c>
       <c r="B32" t="n">
-        <v>78781</v>
+        <v>91367</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,21 +3665,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592696</v>
+        <v>592680</v>
       </c>
       <c r="R32" t="n">
-        <v>7031869</v>
+        <v>7031902</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127482742</v>
+        <v>127480942</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
+        <v>78787</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,39 +3762,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592649</v>
+        <v>592696</v>
       </c>
       <c r="R33" t="n">
-        <v>7031888</v>
+        <v>7031869</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3827,11 +3822,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3858,10 +3848,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127482952</v>
+        <v>127482742</v>
       </c>
       <c r="B34" t="n">
-        <v>91359</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3869,34 +3859,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592680</v>
+        <v>592649</v>
       </c>
       <c r="R34" t="n">
-        <v>7031902</v>
+        <v>7031888</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3929,6 +3924,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3958,7 +3958,7 @@
         <v>127486071</v>
       </c>
       <c r="B35" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>127483251</v>
       </c>
       <c r="B36" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4149,32 +4149,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127484950</v>
+        <v>127481330</v>
       </c>
       <c r="B37" t="n">
-        <v>91502</v>
+        <v>75153</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592522</v>
+        <v>592752</v>
       </c>
       <c r="R37" t="n">
-        <v>7031851</v>
+        <v>7031965</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4246,10 +4246,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127481330</v>
+        <v>127483235</v>
       </c>
       <c r="B38" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592752</v>
+        <v>592635</v>
       </c>
       <c r="R38" t="n">
-        <v>7031965</v>
+        <v>7031936</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4343,32 +4343,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127483235</v>
+        <v>127484950</v>
       </c>
       <c r="B39" t="n">
-        <v>75147</v>
+        <v>91510</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592635</v>
+        <v>592522</v>
       </c>
       <c r="R39" t="n">
-        <v>7031936</v>
+        <v>7031851</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4443,7 +4443,7 @@
         <v>127482368</v>
       </c>
       <c r="B40" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4537,10 +4537,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127482261</v>
+        <v>127483057</v>
       </c>
       <c r="B41" t="n">
-        <v>75139</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4548,21 +4548,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592559</v>
+        <v>592679</v>
       </c>
       <c r="R41" t="n">
-        <v>7031935</v>
+        <v>7031907</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4634,10 +4634,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127483057</v>
+        <v>127482261</v>
       </c>
       <c r="B42" t="n">
-        <v>79023</v>
+        <v>75145</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592679</v>
+        <v>592559</v>
       </c>
       <c r="R42" t="n">
-        <v>7031907</v>
+        <v>7031935</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127483367</v>
+        <v>127482288</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,34 +1100,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592559</v>
+        <v>592543</v>
       </c>
       <c r="R6" t="n">
-        <v>7031863</v>
+        <v>7031902</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,6 +1165,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1186,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127482288</v>
+        <v>127483367</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,39 +1207,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592543</v>
+        <v>592559</v>
       </c>
       <c r="R7" t="n">
-        <v>7031902</v>
+        <v>7031863</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1262,11 +1267,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,7 +1393,7 @@
         <v>127481815</v>
       </c>
       <c r="B9" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127484400</v>
+        <v>127481272</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,34 +1498,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592527</v>
+        <v>592774</v>
       </c>
       <c r="R10" t="n">
-        <v>7031858</v>
+        <v>7031974</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1558,6 +1563,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1584,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127481272</v>
+        <v>127484400</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,39 +1605,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592774</v>
+        <v>592527</v>
       </c>
       <c r="R11" t="n">
-        <v>7031974</v>
+        <v>7031858</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1660,11 +1665,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,7 +1694,7 @@
         <v>127482820</v>
       </c>
       <c r="B12" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127481183</v>
+        <v>127481620</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>75145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592727</v>
+        <v>592695</v>
       </c>
       <c r="R13" t="n">
-        <v>7031939</v>
+        <v>7031932</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127483297</v>
+        <v>127481183</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592600</v>
+        <v>592727</v>
       </c>
       <c r="R14" t="n">
-        <v>7031907</v>
+        <v>7031939</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127481620</v>
+        <v>127483297</v>
       </c>
       <c r="B15" t="n">
-        <v>75145</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592695</v>
+        <v>592600</v>
       </c>
       <c r="R15" t="n">
-        <v>7031932</v>
+        <v>7031907</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127480961</v>
+        <v>127482329</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>91350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592704</v>
+        <v>592559</v>
       </c>
       <c r="R21" t="n">
-        <v>7031881</v>
+        <v>7031898</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127482329</v>
+        <v>127480961</v>
       </c>
       <c r="B22" t="n">
-        <v>91349</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592559</v>
+        <v>592704</v>
       </c>
       <c r="R22" t="n">
-        <v>7031898</v>
+        <v>7031881</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2869,10 +2869,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127481753</v>
+        <v>127483314</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>91350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2880,21 +2880,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592670</v>
+        <v>592591</v>
       </c>
       <c r="R24" t="n">
-        <v>7031932</v>
+        <v>7031906</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2969,7 +2969,7 @@
         <v>127482171</v>
       </c>
       <c r="B25" t="n">
-        <v>91923</v>
+        <v>91924</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,10 +3063,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127483314</v>
+        <v>127481753</v>
       </c>
       <c r="B26" t="n">
-        <v>91349</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3074,21 +3074,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592591</v>
+        <v>592670</v>
       </c>
       <c r="R26" t="n">
-        <v>7031906</v>
+        <v>7031932</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3160,32 +3160,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127482437</v>
+        <v>127480974</v>
       </c>
       <c r="B27" t="n">
-        <v>91314</v>
+        <v>92833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592588</v>
+        <v>592705</v>
       </c>
       <c r="R27" t="n">
-        <v>7031892</v>
+        <v>7031887</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127480974</v>
+        <v>127482437</v>
       </c>
       <c r="B28" t="n">
-        <v>92832</v>
+        <v>91315</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592705</v>
+        <v>592588</v>
       </c>
       <c r="R28" t="n">
-        <v>7031887</v>
+        <v>7031892</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3354,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127481075</v>
+        <v>127483311</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>88753</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592724</v>
+        <v>592598</v>
       </c>
       <c r="R29" t="n">
-        <v>7031919</v>
+        <v>7031904</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3451,54 +3451,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127482031</v>
+        <v>127481075</v>
       </c>
       <c r="B30" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592643</v>
+        <v>592724</v>
       </c>
       <c r="R30" t="n">
-        <v>7031927</v>
+        <v>7031919</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3557,45 +3548,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127483311</v>
+        <v>127482031</v>
       </c>
       <c r="B31" t="n">
-        <v>88752</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592598</v>
+        <v>592643</v>
       </c>
       <c r="R31" t="n">
-        <v>7031904</v>
+        <v>7031927</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127482952</v>
+        <v>127482742</v>
       </c>
       <c r="B32" t="n">
-        <v>91367</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,34 +3665,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592680</v>
+        <v>592649</v>
       </c>
       <c r="R32" t="n">
-        <v>7031902</v>
+        <v>7031888</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3725,6 +3730,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3751,10 +3761,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127480942</v>
+        <v>127482952</v>
       </c>
       <c r="B33" t="n">
-        <v>78787</v>
+        <v>91368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,21 +3772,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3786,10 +3796,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592696</v>
+        <v>592680</v>
       </c>
       <c r="R33" t="n">
-        <v>7031869</v>
+        <v>7031902</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3848,10 +3858,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127482742</v>
+        <v>127480942</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>78787</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3859,39 +3869,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592649</v>
+        <v>592696</v>
       </c>
       <c r="R34" t="n">
-        <v>7031888</v>
+        <v>7031869</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3924,11 +3929,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3958,7 +3958,7 @@
         <v>127486071</v>
       </c>
       <c r="B35" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4149,32 +4149,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127481330</v>
+        <v>127484950</v>
       </c>
       <c r="B37" t="n">
-        <v>75153</v>
+        <v>91511</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592752</v>
+        <v>592522</v>
       </c>
       <c r="R37" t="n">
-        <v>7031965</v>
+        <v>7031851</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4246,7 +4246,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127483235</v>
+        <v>127481330</v>
       </c>
       <c r="B38" t="n">
         <v>75153</v>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592635</v>
+        <v>592752</v>
       </c>
       <c r="R38" t="n">
-        <v>7031936</v>
+        <v>7031965</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4343,32 +4343,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127484950</v>
+        <v>127483235</v>
       </c>
       <c r="B39" t="n">
-        <v>91510</v>
+        <v>75153</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592522</v>
+        <v>592635</v>
       </c>
       <c r="R39" t="n">
-        <v>7031851</v>
+        <v>7031936</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4537,10 +4537,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127483057</v>
+        <v>127482261</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>75145</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4548,21 +4548,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592679</v>
+        <v>592559</v>
       </c>
       <c r="R41" t="n">
-        <v>7031907</v>
+        <v>7031935</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4634,10 +4634,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127482261</v>
+        <v>127483057</v>
       </c>
       <c r="B42" t="n">
-        <v>75145</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592559</v>
+        <v>592679</v>
       </c>
       <c r="R42" t="n">
-        <v>7031935</v>
+        <v>7031907</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127482288</v>
+        <v>127483367</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,39 +1100,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592543</v>
+        <v>592559</v>
       </c>
       <c r="R6" t="n">
-        <v>7031902</v>
+        <v>7031863</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1165,11 +1160,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127483367</v>
+        <v>127482288</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1207,34 +1197,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592559</v>
+        <v>592543</v>
       </c>
       <c r="R7" t="n">
-        <v>7031863</v>
+        <v>7031902</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1267,6 +1262,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127481815</v>
+        <v>127481272</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,34 +1401,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592689</v>
+        <v>592774</v>
       </c>
       <c r="R9" t="n">
-        <v>7031931</v>
+        <v>7031974</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1461,6 +1466,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1487,10 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127481272</v>
+        <v>127481815</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,39 +1508,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592774</v>
+        <v>592689</v>
       </c>
       <c r="R10" t="n">
-        <v>7031974</v>
+        <v>7031931</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1563,11 +1568,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127482512</v>
+        <v>127482577</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592609</v>
+        <v>592617</v>
       </c>
       <c r="R18" t="n">
-        <v>7031869</v>
+        <v>7031890</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2384,7 +2384,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127482277</v>
+        <v>127482512</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592536</v>
+        <v>592609</v>
       </c>
       <c r="R19" t="n">
-        <v>7031910</v>
+        <v>7031869</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127482577</v>
+        <v>127482277</v>
       </c>
       <c r="B20" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592617</v>
+        <v>592536</v>
       </c>
       <c r="R20" t="n">
-        <v>7031890</v>
+        <v>7031910</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127483314</v>
+        <v>127482171</v>
       </c>
       <c r="B24" t="n">
-        <v>91350</v>
+        <v>91924</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592591</v>
+        <v>592610</v>
       </c>
       <c r="R24" t="n">
-        <v>7031906</v>
+        <v>7031932</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2966,32 +2966,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127482171</v>
+        <v>127483314</v>
       </c>
       <c r="B25" t="n">
-        <v>91924</v>
+        <v>91350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592610</v>
+        <v>592591</v>
       </c>
       <c r="R25" t="n">
-        <v>7031932</v>
+        <v>7031906</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3354,45 +3354,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127483311</v>
+        <v>127482031</v>
       </c>
       <c r="B29" t="n">
-        <v>88753</v>
+        <v>98468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592598</v>
+        <v>592643</v>
       </c>
       <c r="R29" t="n">
-        <v>7031904</v>
+        <v>7031927</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3451,10 +3460,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127481075</v>
+        <v>127483311</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>88753</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3462,21 +3471,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3495,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592724</v>
+        <v>592598</v>
       </c>
       <c r="R30" t="n">
-        <v>7031919</v>
+        <v>7031904</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3548,54 +3557,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127482031</v>
+        <v>127481075</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592643</v>
+        <v>592724</v>
       </c>
       <c r="R31" t="n">
-        <v>7031927</v>
+        <v>7031919</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127482742</v>
+        <v>127482952</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>91368</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,39 +3665,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592649</v>
+        <v>592680</v>
       </c>
       <c r="R32" t="n">
-        <v>7031888</v>
+        <v>7031902</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3730,11 +3725,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3761,10 +3751,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127482952</v>
+        <v>127480942</v>
       </c>
       <c r="B33" t="n">
-        <v>91368</v>
+        <v>78787</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3772,21 +3762,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3796,10 +3786,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592680</v>
+        <v>592696</v>
       </c>
       <c r="R33" t="n">
-        <v>7031902</v>
+        <v>7031869</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3858,10 +3848,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127480942</v>
+        <v>127482742</v>
       </c>
       <c r="B34" t="n">
-        <v>78787</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3869,34 +3859,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592696</v>
+        <v>592649</v>
       </c>
       <c r="R34" t="n">
-        <v>7031869</v>
+        <v>7031888</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3929,6 +3924,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4149,32 +4149,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127484950</v>
+        <v>127481330</v>
       </c>
       <c r="B37" t="n">
-        <v>91511</v>
+        <v>75153</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592522</v>
+        <v>592752</v>
       </c>
       <c r="R37" t="n">
-        <v>7031851</v>
+        <v>7031965</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4246,7 +4246,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127481330</v>
+        <v>127483235</v>
       </c>
       <c r="B38" t="n">
         <v>75153</v>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592752</v>
+        <v>592635</v>
       </c>
       <c r="R38" t="n">
-        <v>7031965</v>
+        <v>7031936</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4343,32 +4343,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127483235</v>
+        <v>127484950</v>
       </c>
       <c r="B39" t="n">
-        <v>75153</v>
+        <v>91511</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592635</v>
+        <v>592522</v>
       </c>
       <c r="R39" t="n">
-        <v>7031936</v>
+        <v>7031851</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4537,10 +4537,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127482261</v>
+        <v>127483057</v>
       </c>
       <c r="B41" t="n">
-        <v>75145</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4548,21 +4548,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592559</v>
+        <v>592679</v>
       </c>
       <c r="R41" t="n">
-        <v>7031935</v>
+        <v>7031907</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4634,10 +4634,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127483057</v>
+        <v>127482261</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>75145</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592679</v>
+        <v>592559</v>
       </c>
       <c r="R42" t="n">
-        <v>7031907</v>
+        <v>7031935</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -1390,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127481272</v>
+        <v>127481815</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>91351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,39 +1401,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592774</v>
+        <v>592689</v>
       </c>
       <c r="R9" t="n">
-        <v>7031974</v>
+        <v>7031931</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1466,11 +1461,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1497,10 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127481815</v>
+        <v>127484400</v>
       </c>
       <c r="B10" t="n">
-        <v>91350</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1508,21 +1498,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1532,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592689</v>
+        <v>592527</v>
       </c>
       <c r="R10" t="n">
-        <v>7031931</v>
+        <v>7031858</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1594,10 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127484400</v>
+        <v>127481272</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,34 +1595,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592527</v>
+        <v>592774</v>
       </c>
       <c r="R11" t="n">
-        <v>7031858</v>
+        <v>7031974</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1665,6 +1660,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,7 +1694,7 @@
         <v>127482820</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         <v>127482329</v>
       </c>
       <c r="B21" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>127482171</v>
       </c>
       <c r="B24" t="n">
-        <v>91924</v>
+        <v>91925</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>127483314</v>
       </c>
       <c r="B25" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>127480974</v>
       </c>
       <c r="B27" t="n">
-        <v>92833</v>
+        <v>92834</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>127482437</v>
       </c>
       <c r="B28" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,54 +3354,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127482031</v>
+        <v>127483311</v>
       </c>
       <c r="B29" t="n">
-        <v>98468</v>
+        <v>88754</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592643</v>
+        <v>592598</v>
       </c>
       <c r="R29" t="n">
-        <v>7031927</v>
+        <v>7031904</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3460,10 +3451,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127483311</v>
+        <v>127481075</v>
       </c>
       <c r="B30" t="n">
-        <v>88753</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3471,21 +3462,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3495,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592598</v>
+        <v>592724</v>
       </c>
       <c r="R30" t="n">
-        <v>7031904</v>
+        <v>7031919</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3557,45 +3548,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127481075</v>
+        <v>127482031</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592724</v>
+        <v>592643</v>
       </c>
       <c r="R31" t="n">
-        <v>7031919</v>
+        <v>7031927</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127482952</v>
+        <v>127482742</v>
       </c>
       <c r="B32" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,34 +3665,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592680</v>
+        <v>592649</v>
       </c>
       <c r="R32" t="n">
-        <v>7031902</v>
+        <v>7031888</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3725,6 +3730,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3751,10 +3761,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127480942</v>
+        <v>127482952</v>
       </c>
       <c r="B33" t="n">
-        <v>78787</v>
+        <v>91369</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,21 +3772,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3786,10 +3796,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592696</v>
+        <v>592680</v>
       </c>
       <c r="R33" t="n">
-        <v>7031869</v>
+        <v>7031902</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3848,10 +3858,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127482742</v>
+        <v>127480942</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>78787</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3859,39 +3869,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592649</v>
+        <v>592696</v>
       </c>
       <c r="R34" t="n">
-        <v>7031888</v>
+        <v>7031869</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3924,11 +3929,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3958,7 +3958,7 @@
         <v>127486071</v>
       </c>
       <c r="B35" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4149,32 +4149,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127481330</v>
+        <v>127484950</v>
       </c>
       <c r="B37" t="n">
-        <v>75153</v>
+        <v>91512</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592752</v>
+        <v>592522</v>
       </c>
       <c r="R37" t="n">
-        <v>7031965</v>
+        <v>7031851</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4246,7 +4246,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127483235</v>
+        <v>127481330</v>
       </c>
       <c r="B38" t="n">
         <v>75153</v>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592635</v>
+        <v>592752</v>
       </c>
       <c r="R38" t="n">
-        <v>7031936</v>
+        <v>7031965</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4343,32 +4343,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127484950</v>
+        <v>127483235</v>
       </c>
       <c r="B39" t="n">
-        <v>91511</v>
+        <v>75153</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592522</v>
+        <v>592635</v>
       </c>
       <c r="R39" t="n">
-        <v>7031851</v>
+        <v>7031936</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -1390,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127481815</v>
+        <v>127484400</v>
       </c>
       <c r="B9" t="n">
-        <v>91351</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,21 +1401,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592689</v>
+        <v>592527</v>
       </c>
       <c r="R9" t="n">
-        <v>7031931</v>
+        <v>7031858</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127484400</v>
+        <v>127481815</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,21 +1498,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592527</v>
+        <v>592689</v>
       </c>
       <c r="R10" t="n">
-        <v>7031858</v>
+        <v>7031931</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1694,7 +1694,7 @@
         <v>127482820</v>
       </c>
       <c r="B12" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127482577</v>
+        <v>127482512</v>
       </c>
       <c r="B18" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592617</v>
+        <v>592609</v>
       </c>
       <c r="R18" t="n">
-        <v>7031890</v>
+        <v>7031869</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2384,7 +2384,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127482512</v>
+        <v>127482277</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592609</v>
+        <v>592536</v>
       </c>
       <c r="R19" t="n">
-        <v>7031869</v>
+        <v>7031910</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127482277</v>
+        <v>127482577</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592536</v>
+        <v>592617</v>
       </c>
       <c r="R20" t="n">
-        <v>7031910</v>
+        <v>7031890</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127482329</v>
+        <v>127480961</v>
       </c>
       <c r="B21" t="n">
-        <v>91351</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592559</v>
+        <v>592704</v>
       </c>
       <c r="R21" t="n">
-        <v>7031898</v>
+        <v>7031881</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127480961</v>
+        <v>127482329</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592704</v>
+        <v>592559</v>
       </c>
       <c r="R22" t="n">
-        <v>7031881</v>
+        <v>7031898</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127482171</v>
+        <v>127481753</v>
       </c>
       <c r="B24" t="n">
-        <v>91925</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592610</v>
+        <v>592670</v>
       </c>
       <c r="R24" t="n">
         <v>7031932</v>
@@ -2966,32 +2966,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127483314</v>
+        <v>127482171</v>
       </c>
       <c r="B25" t="n">
-        <v>91351</v>
+        <v>91926</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592591</v>
+        <v>592610</v>
       </c>
       <c r="R25" t="n">
-        <v>7031906</v>
+        <v>7031932</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3063,10 +3063,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127481753</v>
+        <v>127483314</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3074,21 +3074,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592670</v>
+        <v>592591</v>
       </c>
       <c r="R26" t="n">
-        <v>7031932</v>
+        <v>7031906</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3163,7 +3163,7 @@
         <v>127480974</v>
       </c>
       <c r="B27" t="n">
-        <v>92834</v>
+        <v>92835</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>127482437</v>
       </c>
       <c r="B28" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>127483311</v>
       </c>
       <c r="B29" t="n">
-        <v>88754</v>
+        <v>88755</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>127482031</v>
       </c>
       <c r="B31" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127482742</v>
+        <v>127480942</v>
       </c>
       <c r="B32" t="n">
-        <v>57672</v>
+        <v>78787</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,39 +3665,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592649</v>
+        <v>592696</v>
       </c>
       <c r="R32" t="n">
-        <v>7031888</v>
+        <v>7031869</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3730,11 +3725,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3764,7 +3754,7 @@
         <v>127482952</v>
       </c>
       <c r="B33" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3858,10 +3848,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127480942</v>
+        <v>127482742</v>
       </c>
       <c r="B34" t="n">
-        <v>78787</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3869,34 +3859,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592696</v>
+        <v>592649</v>
       </c>
       <c r="R34" t="n">
-        <v>7031869</v>
+        <v>7031888</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3929,6 +3924,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3958,7 +3958,7 @@
         <v>127486071</v>
       </c>
       <c r="B35" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4149,32 +4149,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127484950</v>
+        <v>127481330</v>
       </c>
       <c r="B37" t="n">
-        <v>91512</v>
+        <v>75153</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592522</v>
+        <v>592752</v>
       </c>
       <c r="R37" t="n">
-        <v>7031851</v>
+        <v>7031965</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4246,7 +4246,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127481330</v>
+        <v>127483235</v>
       </c>
       <c r="B38" t="n">
         <v>75153</v>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592752</v>
+        <v>592635</v>
       </c>
       <c r="R38" t="n">
-        <v>7031965</v>
+        <v>7031936</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4343,32 +4343,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127483235</v>
+        <v>127484950</v>
       </c>
       <c r="B39" t="n">
-        <v>75153</v>
+        <v>91513</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592635</v>
+        <v>592522</v>
       </c>
       <c r="R39" t="n">
-        <v>7031936</v>
+        <v>7031851</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4440,10 +4440,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127482368</v>
+        <v>127482261</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>75145</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4451,21 +4451,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592569</v>
+        <v>592559</v>
       </c>
       <c r="R40" t="n">
-        <v>7031901</v>
+        <v>7031935</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4537,7 +4537,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127483057</v>
+        <v>127482368</v>
       </c>
       <c r="B41" t="n">
         <v>79029</v>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592679</v>
+        <v>592569</v>
       </c>
       <c r="R41" t="n">
-        <v>7031907</v>
+        <v>7031901</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4634,10 +4634,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127482261</v>
+        <v>127483057</v>
       </c>
       <c r="B42" t="n">
-        <v>75145</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592559</v>
+        <v>592679</v>
       </c>
       <c r="R42" t="n">
-        <v>7031935</v>
+        <v>7031907</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -1487,10 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127481815</v>
+        <v>127481272</v>
       </c>
       <c r="B10" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,34 +1498,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592689</v>
+        <v>592774</v>
       </c>
       <c r="R10" t="n">
-        <v>7031931</v>
+        <v>7031974</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1558,6 +1563,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1584,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127481272</v>
+        <v>127481815</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,39 +1605,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592774</v>
+        <v>592689</v>
       </c>
       <c r="R11" t="n">
-        <v>7031974</v>
+        <v>7031931</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1660,11 +1665,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127481620</v>
+        <v>127481183</v>
       </c>
       <c r="B13" t="n">
-        <v>75145</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592695</v>
+        <v>592727</v>
       </c>
       <c r="R13" t="n">
-        <v>7031932</v>
+        <v>7031939</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127481183</v>
+        <v>127483297</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592727</v>
+        <v>592600</v>
       </c>
       <c r="R14" t="n">
-        <v>7031939</v>
+        <v>7031907</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127483297</v>
+        <v>127481620</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>75145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592600</v>
+        <v>592695</v>
       </c>
       <c r="R15" t="n">
-        <v>7031907</v>
+        <v>7031932</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127482512</v>
+        <v>127482577</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592609</v>
+        <v>592617</v>
       </c>
       <c r="R18" t="n">
-        <v>7031869</v>
+        <v>7031890</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2384,7 +2384,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127482277</v>
+        <v>127482512</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592536</v>
+        <v>592609</v>
       </c>
       <c r="R19" t="n">
-        <v>7031910</v>
+        <v>7031869</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127482577</v>
+        <v>127482277</v>
       </c>
       <c r="B20" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592617</v>
+        <v>592536</v>
       </c>
       <c r="R20" t="n">
-        <v>7031890</v>
+        <v>7031910</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127480961</v>
+        <v>127482329</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592704</v>
+        <v>592559</v>
       </c>
       <c r="R21" t="n">
-        <v>7031881</v>
+        <v>7031898</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127482329</v>
+        <v>127480961</v>
       </c>
       <c r="B22" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592559</v>
+        <v>592704</v>
       </c>
       <c r="R22" t="n">
-        <v>7031898</v>
+        <v>7031881</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2869,32 +2869,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127481753</v>
+        <v>127482171</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>91926</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592670</v>
+        <v>592610</v>
       </c>
       <c r="R24" t="n">
         <v>7031932</v>
@@ -2966,32 +2966,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127482171</v>
+        <v>127483314</v>
       </c>
       <c r="B25" t="n">
-        <v>91926</v>
+        <v>91352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592610</v>
+        <v>592591</v>
       </c>
       <c r="R25" t="n">
-        <v>7031932</v>
+        <v>7031906</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3063,10 +3063,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127483314</v>
+        <v>127481753</v>
       </c>
       <c r="B26" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3074,21 +3074,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592591</v>
+        <v>592670</v>
       </c>
       <c r="R26" t="n">
-        <v>7031906</v>
+        <v>7031932</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3160,32 +3160,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127480974</v>
+        <v>127482437</v>
       </c>
       <c r="B27" t="n">
-        <v>92835</v>
+        <v>91317</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3195,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592705</v>
+        <v>592588</v>
       </c>
       <c r="R27" t="n">
-        <v>7031887</v>
+        <v>7031892</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3257,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127482437</v>
+        <v>127480974</v>
       </c>
       <c r="B28" t="n">
-        <v>91317</v>
+        <v>92835</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592588</v>
+        <v>592705</v>
       </c>
       <c r="R28" t="n">
-        <v>7031892</v>
+        <v>7031887</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3354,45 +3354,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127483311</v>
+        <v>127482031</v>
       </c>
       <c r="B29" t="n">
-        <v>88755</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592598</v>
+        <v>592643</v>
       </c>
       <c r="R29" t="n">
-        <v>7031904</v>
+        <v>7031927</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3548,54 +3557,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127482031</v>
+        <v>127483311</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>88755</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592643</v>
+        <v>592598</v>
       </c>
       <c r="R31" t="n">
-        <v>7031927</v>
+        <v>7031904</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3654,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127480942</v>
+        <v>127482952</v>
       </c>
       <c r="B32" t="n">
-        <v>78787</v>
+        <v>91370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,21 +3665,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592696</v>
+        <v>592680</v>
       </c>
       <c r="R32" t="n">
-        <v>7031869</v>
+        <v>7031902</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127482952</v>
+        <v>127482742</v>
       </c>
       <c r="B33" t="n">
-        <v>91370</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,34 +3762,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592680</v>
+        <v>592649</v>
       </c>
       <c r="R33" t="n">
-        <v>7031902</v>
+        <v>7031888</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3822,6 +3827,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3848,10 +3858,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127482742</v>
+        <v>127480942</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>78787</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3859,39 +3869,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592649</v>
+        <v>592696</v>
       </c>
       <c r="R34" t="n">
-        <v>7031888</v>
+        <v>7031869</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3924,11 +3929,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4149,32 +4149,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127481330</v>
+        <v>127484950</v>
       </c>
       <c r="B37" t="n">
-        <v>75153</v>
+        <v>91513</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592752</v>
+        <v>592522</v>
       </c>
       <c r="R37" t="n">
-        <v>7031965</v>
+        <v>7031851</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4343,32 +4343,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127484950</v>
+        <v>127481330</v>
       </c>
       <c r="B39" t="n">
-        <v>91513</v>
+        <v>75153</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592522</v>
+        <v>592752</v>
       </c>
       <c r="R39" t="n">
-        <v>7031851</v>
+        <v>7031965</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -4246,7 +4246,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127483235</v>
+        <v>127481330</v>
       </c>
       <c r="B38" t="n">
         <v>75153</v>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592635</v>
+        <v>592752</v>
       </c>
       <c r="R38" t="n">
-        <v>7031936</v>
+        <v>7031965</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127481330</v>
+        <v>127483235</v>
       </c>
       <c r="B39" t="n">
         <v>75153</v>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592752</v>
+        <v>592635</v>
       </c>
       <c r="R39" t="n">
-        <v>7031965</v>
+        <v>7031936</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4440,10 +4440,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127482261</v>
+        <v>127482368</v>
       </c>
       <c r="B40" t="n">
-        <v>75145</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4451,21 +4451,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592559</v>
+        <v>592569</v>
       </c>
       <c r="R40" t="n">
-        <v>7031935</v>
+        <v>7031901</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4537,7 +4537,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127482368</v>
+        <v>127483057</v>
       </c>
       <c r="B41" t="n">
         <v>79029</v>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592569</v>
+        <v>592679</v>
       </c>
       <c r="R41" t="n">
-        <v>7031901</v>
+        <v>7031907</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4634,10 +4634,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127483057</v>
+        <v>127482261</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>75145</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592679</v>
+        <v>592559</v>
       </c>
       <c r="R42" t="n">
-        <v>7031907</v>
+        <v>7031935</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127481183</v>
+        <v>127481620</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>75145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592727</v>
+        <v>592695</v>
       </c>
       <c r="R13" t="n">
-        <v>7031939</v>
+        <v>7031932</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127483297</v>
+        <v>127481183</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592600</v>
+        <v>592727</v>
       </c>
       <c r="R14" t="n">
-        <v>7031907</v>
+        <v>7031939</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127481620</v>
+        <v>127483297</v>
       </c>
       <c r="B15" t="n">
-        <v>75145</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592695</v>
+        <v>592600</v>
       </c>
       <c r="R15" t="n">
-        <v>7031932</v>
+        <v>7031907</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -3354,54 +3354,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127482031</v>
+        <v>127481075</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592643</v>
+        <v>592724</v>
       </c>
       <c r="R29" t="n">
-        <v>7031927</v>
+        <v>7031919</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3460,10 +3451,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127481075</v>
+        <v>127483311</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>88755</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3471,21 +3462,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3495,10 +3486,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592724</v>
+        <v>592598</v>
       </c>
       <c r="R30" t="n">
-        <v>7031919</v>
+        <v>7031904</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3557,45 +3548,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127483311</v>
+        <v>127482031</v>
       </c>
       <c r="B31" t="n">
-        <v>88755</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592598</v>
+        <v>592643</v>
       </c>
       <c r="R31" t="n">
-        <v>7031904</v>
+        <v>7031927</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3751,10 +3751,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127482742</v>
+        <v>127480942</v>
       </c>
       <c r="B33" t="n">
-        <v>57672</v>
+        <v>78787</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3762,39 +3762,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592649</v>
+        <v>592696</v>
       </c>
       <c r="R33" t="n">
-        <v>7031888</v>
+        <v>7031869</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3827,11 +3822,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3858,10 +3848,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127480942</v>
+        <v>127482742</v>
       </c>
       <c r="B34" t="n">
-        <v>78787</v>
+        <v>57672</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3869,34 +3859,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592696</v>
+        <v>592649</v>
       </c>
       <c r="R34" t="n">
-        <v>7031869</v>
+        <v>7031888</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3929,6 +3924,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -1788,10 +1788,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127481620</v>
+        <v>127481183</v>
       </c>
       <c r="B13" t="n">
-        <v>75145</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592695</v>
+        <v>592727</v>
       </c>
       <c r="R13" t="n">
-        <v>7031932</v>
+        <v>7031939</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127481183</v>
+        <v>127483297</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592727</v>
+        <v>592600</v>
       </c>
       <c r="R14" t="n">
-        <v>7031939</v>
+        <v>7031907</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1982,10 +1982,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127483297</v>
+        <v>127481620</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>75145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592600</v>
+        <v>592695</v>
       </c>
       <c r="R15" t="n">
-        <v>7031907</v>
+        <v>7031932</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -4149,32 +4149,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127484950</v>
+        <v>127481330</v>
       </c>
       <c r="B37" t="n">
-        <v>91513</v>
+        <v>75153</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1503</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592522</v>
+        <v>592752</v>
       </c>
       <c r="R37" t="n">
-        <v>7031851</v>
+        <v>7031965</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4246,32 +4246,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127481330</v>
+        <v>127484950</v>
       </c>
       <c r="B38" t="n">
-        <v>75153</v>
+        <v>91513</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4281,10 +4281,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592752</v>
+        <v>592522</v>
       </c>
       <c r="R38" t="n">
-        <v>7031965</v>
+        <v>7031851</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4440,10 +4440,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127482368</v>
+        <v>127482261</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>75145</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4451,21 +4451,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592569</v>
+        <v>592559</v>
       </c>
       <c r="R40" t="n">
-        <v>7031901</v>
+        <v>7031935</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4537,7 +4537,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127483057</v>
+        <v>127482368</v>
       </c>
       <c r="B41" t="n">
         <v>79029</v>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592679</v>
+        <v>592569</v>
       </c>
       <c r="R41" t="n">
-        <v>7031907</v>
+        <v>7031901</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4634,10 +4634,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127482261</v>
+        <v>127483057</v>
       </c>
       <c r="B42" t="n">
-        <v>75145</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592559</v>
+        <v>592679</v>
       </c>
       <c r="R42" t="n">
-        <v>7031935</v>
+        <v>7031907</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119484566</v>
+        <v>127481318</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Småmyrorna, Småmyrorna, Ång</t>
+          <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592562</v>
+        <v>592760</v>
       </c>
       <c r="R2" t="n">
-        <v>7031903</v>
+        <v>7031963</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119483889</v>
+        <v>127481620</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Småmyrorna, Småmyrorna, Ång</t>
+          <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592669</v>
+        <v>592695</v>
       </c>
       <c r="R3" t="n">
-        <v>7031894</v>
+        <v>7031932</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119496044</v>
+        <v>127482261</v>
       </c>
       <c r="B4" t="n">
-        <v>4915</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,42 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101994</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspbarkgnagare</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Xyletinus tremulicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Y.Kangas, 1958</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sjöberget, Ång</t>
+          <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592666</v>
+        <v>592559</v>
       </c>
       <c r="R4" t="n">
-        <v>7031894</v>
+        <v>7031935</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,17 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Osäker artbestämning. Kläckhål i barken på döende stående asp.</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -973,29 +948,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127482681</v>
+        <v>127482577</v>
       </c>
       <c r="B5" t="n">
-        <v>78696</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592639</v>
+        <v>592617</v>
       </c>
       <c r="R5" t="n">
-        <v>7031884</v>
+        <v>7031890</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1089,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127483367</v>
+        <v>127482681</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592559</v>
+        <v>592639</v>
       </c>
       <c r="R6" t="n">
-        <v>7031863</v>
+        <v>7031884</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1186,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127482288</v>
+        <v>127483311</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>89292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,39 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592543</v>
+        <v>592598</v>
       </c>
       <c r="R7" t="n">
-        <v>7031902</v>
+        <v>7031904</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1262,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1293,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127481318</v>
+        <v>127482171</v>
       </c>
       <c r="B8" t="n">
-        <v>75145</v>
+        <v>92509</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592760</v>
+        <v>592610</v>
       </c>
       <c r="R8" t="n">
-        <v>7031963</v>
+        <v>7031932</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1390,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127484400</v>
+        <v>119484566</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sjömyran, Sjömyran, Ång</t>
+          <t>Småmyrorna, Småmyrorna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592527</v>
+        <v>592562</v>
       </c>
       <c r="R9" t="n">
-        <v>7031858</v>
+        <v>7031903</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1455,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1475,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127481272</v>
+        <v>127481815</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1498,39 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592774</v>
+        <v>592689</v>
       </c>
       <c r="R10" t="n">
-        <v>7031974</v>
+        <v>7031931</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1563,11 +1522,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1594,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127481815</v>
+        <v>127482329</v>
       </c>
       <c r="B11" t="n">
-        <v>91352</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592689</v>
+        <v>592559</v>
       </c>
       <c r="R11" t="n">
-        <v>7031931</v>
+        <v>7031898</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1694,7 +1648,7 @@
         <v>127482820</v>
       </c>
       <c r="B12" t="n">
-        <v>91352</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127481183</v>
+        <v>127483314</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1799,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1823,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592727</v>
+        <v>592591</v>
       </c>
       <c r="R13" t="n">
-        <v>7031939</v>
+        <v>7031906</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1885,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127483297</v>
+        <v>127483251</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592600</v>
+        <v>592625</v>
       </c>
       <c r="R14" t="n">
-        <v>7031907</v>
+        <v>7031937</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1982,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127481620</v>
+        <v>127484950</v>
       </c>
       <c r="B15" t="n">
-        <v>75145</v>
+        <v>92083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592695</v>
+        <v>592522</v>
       </c>
       <c r="R15" t="n">
-        <v>7031932</v>
+        <v>7031851</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2079,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127480832</v>
+        <v>127480974</v>
       </c>
       <c r="B16" t="n">
-        <v>57832</v>
+        <v>91962</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,43 +2044,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592683</v>
+        <v>592705</v>
       </c>
       <c r="R16" t="n">
-        <v>7031889</v>
+        <v>7031887</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2185,50 +2130,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127481178</v>
+        <v>127482437</v>
       </c>
       <c r="B17" t="n">
-        <v>57669</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592727</v>
+        <v>592588</v>
       </c>
       <c r="R17" t="n">
-        <v>7031939</v>
+        <v>7031892</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2287,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127482577</v>
+        <v>127486071</v>
       </c>
       <c r="B18" t="n">
-        <v>78696</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592617</v>
+        <v>592561</v>
       </c>
       <c r="R18" t="n">
-        <v>7031890</v>
+        <v>7031869</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2384,14 +2324,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127482512</v>
+        <v>127480763</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2419,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592609</v>
+        <v>592667</v>
       </c>
       <c r="R19" t="n">
-        <v>7031869</v>
+        <v>7031888</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2481,14 +2421,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127482277</v>
+        <v>127480961</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2516,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592536</v>
+        <v>592704</v>
       </c>
       <c r="R20" t="n">
-        <v>7031910</v>
+        <v>7031881</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2578,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127482329</v>
+        <v>127481075</v>
       </c>
       <c r="B21" t="n">
-        <v>91352</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592559</v>
+        <v>592724</v>
       </c>
       <c r="R21" t="n">
-        <v>7031898</v>
+        <v>7031919</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2675,14 +2615,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127480961</v>
+        <v>127481183</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2710,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592704</v>
+        <v>592727</v>
       </c>
       <c r="R22" t="n">
-        <v>7031881</v>
+        <v>7031939</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2772,14 +2712,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127480763</v>
+        <v>127481753</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2807,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592667</v>
+        <v>592670</v>
       </c>
       <c r="R23" t="n">
-        <v>7031888</v>
+        <v>7031932</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2869,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127482171</v>
+        <v>127482277</v>
       </c>
       <c r="B24" t="n">
-        <v>91926</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2880,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2904,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592610</v>
+        <v>592536</v>
       </c>
       <c r="R24" t="n">
-        <v>7031932</v>
+        <v>7031910</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2966,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127483314</v>
+        <v>127482368</v>
       </c>
       <c r="B25" t="n">
-        <v>91352</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3001,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592591</v>
+        <v>592569</v>
       </c>
       <c r="R25" t="n">
-        <v>7031906</v>
+        <v>7031901</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3063,14 +3003,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127481753</v>
+        <v>127482512</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3098,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592670</v>
+        <v>592609</v>
       </c>
       <c r="R26" t="n">
-        <v>7031932</v>
+        <v>7031869</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3160,32 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127482437</v>
+        <v>127483057</v>
       </c>
       <c r="B27" t="n">
-        <v>91317</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3195,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592588</v>
+        <v>592679</v>
       </c>
       <c r="R27" t="n">
-        <v>7031892</v>
+        <v>7031907</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3257,32 +3197,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127480974</v>
+        <v>127483297</v>
       </c>
       <c r="B28" t="n">
-        <v>92835</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3292,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592705</v>
+        <v>592600</v>
       </c>
       <c r="R28" t="n">
-        <v>7031887</v>
+        <v>7031907</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3354,14 +3294,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127481075</v>
+        <v>127483367</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3389,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592724</v>
+        <v>592559</v>
       </c>
       <c r="R29" t="n">
-        <v>7031919</v>
+        <v>7031863</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3451,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127483311</v>
+        <v>127484400</v>
       </c>
       <c r="B30" t="n">
-        <v>88755</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3486,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592598</v>
+        <v>592527</v>
       </c>
       <c r="R30" t="n">
-        <v>7031904</v>
+        <v>7031858</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3548,54 +3488,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127482031</v>
+        <v>127481330</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>83307</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592643</v>
+        <v>592752</v>
       </c>
       <c r="R31" t="n">
-        <v>7031927</v>
+        <v>7031965</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3654,10 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127482952</v>
+        <v>127483235</v>
       </c>
       <c r="B32" t="n">
-        <v>91370</v>
+        <v>83307</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,21 +3596,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3689,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592680</v>
+        <v>592635</v>
       </c>
       <c r="R32" t="n">
-        <v>7031902</v>
+        <v>7031936</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3754,7 +3685,7 @@
         <v>127480942</v>
       </c>
       <c r="B33" t="n">
-        <v>78787</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3848,10 +3779,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127482742</v>
+        <v>119483889</v>
       </c>
       <c r="B34" t="n">
-        <v>57672</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3859,42 +3790,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sjömyran, Sjömyran, Ång</t>
+          <t>Småmyrorna, Småmyrorna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592649</v>
+        <v>592669</v>
       </c>
       <c r="R34" t="n">
-        <v>7031888</v>
+        <v>7031894</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3918,17 +3844,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3943,22 +3864,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127486071</v>
+        <v>127481352</v>
       </c>
       <c r="B35" t="n">
-        <v>91317</v>
+        <v>80460</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3966,21 +3887,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6461</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3990,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592561</v>
+        <v>592730</v>
       </c>
       <c r="R35" t="n">
-        <v>7031869</v>
+        <v>7031962</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4052,45 +3973,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127483251</v>
+        <v>127481178</v>
       </c>
       <c r="B36" t="n">
-        <v>82870</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>592625</v>
+        <v>592727</v>
       </c>
       <c r="R36" t="n">
-        <v>7031937</v>
+        <v>7031939</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4149,10 +4075,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127481330</v>
+        <v>127481272</v>
       </c>
       <c r="B37" t="n">
-        <v>75153</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4160,34 +4086,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592752</v>
+        <v>592774</v>
       </c>
       <c r="R37" t="n">
-        <v>7031965</v>
+        <v>7031974</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4220,6 +4151,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4246,45 +4182,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127484950</v>
+        <v>127482288</v>
       </c>
       <c r="B38" t="n">
-        <v>91513</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1503</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592522</v>
+        <v>592543</v>
       </c>
       <c r="R38" t="n">
-        <v>7031851</v>
+        <v>7031902</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4317,6 +4258,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4343,10 +4289,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127483235</v>
+        <v>127482742</v>
       </c>
       <c r="B39" t="n">
-        <v>75153</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4354,34 +4300,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592635</v>
+        <v>592649</v>
       </c>
       <c r="R39" t="n">
-        <v>7031936</v>
+        <v>7031888</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4414,6 +4365,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4440,10 +4396,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127482261</v>
+        <v>119496044</v>
       </c>
       <c r="B40" t="n">
-        <v>75145</v>
+        <v>4924</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4451,37 +4407,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>308</v>
+        <v>101994</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Aspbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Xyletinus tremulicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Y.Kangas, 1958</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sjömyran, Sjömyran, Ång</t>
+          <t>Sjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592559</v>
+        <v>592666</v>
       </c>
       <c r="R40" t="n">
-        <v>7031935</v>
+        <v>7031894</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4505,12 +4466,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning. Kläckhål i barken på döende stående asp.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4519,28 +4485,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127482368</v>
+        <v>127480832</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>58114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4548,34 +4515,43 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592569</v>
+        <v>592683</v>
       </c>
       <c r="R41" t="n">
-        <v>7031901</v>
+        <v>7031889</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4634,45 +4610,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127483057</v>
+        <v>127482031</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sjömyran, Sjömyran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592679</v>
+        <v>592643</v>
       </c>
       <c r="R42" t="n">
-        <v>7031907</v>
+        <v>7031927</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4728,6 +4713,103 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127482798</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Sjömyran, Sjömyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>592651</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7031891</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37489-2025 artfynd.xlsx
+++ b/artfynd/A 37489-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127481318</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127481620</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127482261</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127482577</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127482681</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127483311</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127482171</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119484566</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127481815</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127482329</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127482820</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127483314</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127483251</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127484950</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127480974</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127482437</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127486071</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127480763</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127480961</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127481075</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127481183</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127481753</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127482277</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127482368</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127482512</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127483057</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127483297</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127483367</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127484400</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127481330</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127483235</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127480942</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119483889</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127481352</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4072,6 +4247,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127481178</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4179,6 +4359,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127481272</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4286,6 +4471,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127482288</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4393,6 +4583,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127482742</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4501,6 +4696,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119496044</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4607,6 +4807,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127480832</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4713,6 +4918,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127482031</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4810,8 +5020,57 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127482798</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>